--- a/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="472" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{55087335-0378-4067-8C17-EF6C4D928C29}"/>
+  <xr:revisionPtr revIDLastSave="476" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D2A1CF1-0BB7-4312-A42E-8559B70FEBDB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -190,7 +190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,6 +281,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="43">
     <border>
@@ -828,7 +840,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1060,6 +1072,36 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1087,35 +1129,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3774,77 +3798,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="94">
-        <v>1</v>
-      </c>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="96"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="104">
+        <v>1</v>
+      </c>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="106"/>
       <c r="H1" s="54"/>
       <c r="I1" s="55"/>
-      <c r="J1" s="94">
+      <c r="J1" s="104">
         <v>2</v>
       </c>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="96"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="106"/>
       <c r="O1" s="54"/>
       <c r="P1" s="55"/>
-      <c r="Q1" s="94">
+      <c r="Q1" s="104">
         <v>3</v>
       </c>
-      <c r="R1" s="95"/>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="96"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="106"/>
       <c r="V1" s="54"/>
       <c r="W1" s="55"/>
-      <c r="X1" s="94">
+      <c r="X1" s="104">
         <v>4</v>
       </c>
-      <c r="Y1" s="95"/>
-      <c r="Z1" s="95"/>
-      <c r="AA1" s="95"/>
-      <c r="AB1" s="96"/>
+      <c r="Y1" s="105"/>
+      <c r="Z1" s="105"/>
+      <c r="AA1" s="105"/>
+      <c r="AB1" s="106"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="55"/>
-      <c r="AE1" s="97">
+      <c r="AE1" s="107">
         <v>5</v>
       </c>
-      <c r="AF1" s="98"/>
-      <c r="AG1" s="98"/>
-      <c r="AH1" s="98"/>
-      <c r="AI1" s="99"/>
+      <c r="AF1" s="108"/>
+      <c r="AG1" s="108"/>
+      <c r="AH1" s="108"/>
+      <c r="AI1" s="109"/>
       <c r="AJ1" s="63"/>
       <c r="AK1" s="64"/>
-      <c r="AL1" s="91">
+      <c r="AL1" s="101">
         <v>6</v>
       </c>
-      <c r="AM1" s="92"/>
-      <c r="AN1" s="92"/>
-      <c r="AO1" s="92"/>
-      <c r="AP1" s="93"/>
+      <c r="AM1" s="102"/>
+      <c r="AN1" s="102"/>
+      <c r="AO1" s="102"/>
+      <c r="AP1" s="103"/>
       <c r="AQ1" s="63"/>
       <c r="AR1" s="64"/>
-      <c r="AS1" s="91">
+      <c r="AS1" s="101">
         <v>7</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="93"/>
+      <c r="AT1" s="102"/>
+      <c r="AU1" s="102"/>
+      <c r="AV1" s="102"/>
+      <c r="AW1" s="103"/>
     </row>
     <row r="2" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="A2" s="97" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="107"/>
+      <c r="B2" s="98"/>
       <c r="C2" s="6">
         <v>1</v>
       </c>
@@ -3964,10 +3988,10 @@
       </c>
     </row>
     <row r="3" spans="1:52" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="108" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="109"/>
+      <c r="A3" s="99" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="100"/>
       <c r="C3" s="49">
         <v>45887</v>
       </c>
@@ -4111,7 +4135,7 @@
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A4" s="101" t="s">
+      <c r="A4" s="92" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4166,7 +4190,7 @@
       <c r="AW4" s="39"/>
     </row>
     <row r="5" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="101"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4225,13 +4249,13 @@
       <c r="AW5" s="35"/>
     </row>
     <row r="6" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="102"/>
+      <c r="A6" s="93"/>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="21"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="113"/>
       <c r="F6" s="21"/>
       <c r="G6" s="21"/>
       <c r="H6" s="41"/>
@@ -4284,7 +4308,7 @@
       </c>
     </row>
     <row r="7" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="100" t="s">
+      <c r="A7" s="91" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4348,7 +4372,7 @@
       </c>
     </row>
     <row r="8" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="101"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
@@ -4416,13 +4440,13 @@
       </c>
     </row>
     <row r="9" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="102"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="19"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="H9" s="46"/>
@@ -4476,7 +4500,7 @@
       </c>
     </row>
     <row r="10" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="91" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4540,7 +4564,7 @@
       </c>
     </row>
     <row r="11" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="101"/>
+      <c r="A11" s="92"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -4606,7 +4630,7 @@
       </c>
     </row>
     <row r="12" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="102"/>
+      <c r="A12" s="93"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -4666,7 +4690,7 @@
       </c>
     </row>
     <row r="13" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="100" t="s">
+      <c r="A13" s="91" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -4728,7 +4752,7 @@
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A14" s="101"/>
+      <c r="A14" s="92"/>
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
@@ -4785,7 +4809,7 @@
       <c r="AW14" s="35"/>
     </row>
     <row r="15" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="102"/>
+      <c r="A15" s="93"/>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
@@ -4838,7 +4862,7 @@
       <c r="AW15" s="37"/>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="91" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4893,7 +4917,7 @@
       <c r="AW16" s="39"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A17" s="101"/>
+      <c r="A17" s="92"/>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
@@ -4988,7 +5012,7 @@
       <c r="AW17" s="35"/>
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="102"/>
+      <c r="A18" s="93"/>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
@@ -5041,7 +5065,7 @@
       <c r="AW18" s="37"/>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A19" s="100" t="s">
+      <c r="A19" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -5096,7 +5120,7 @@
       <c r="AW19" s="39"/>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A20" s="101"/>
+      <c r="A20" s="92"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
@@ -5165,7 +5189,7 @@
       <c r="AW20" s="35"/>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="102"/>
+      <c r="A21" s="93"/>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
@@ -5218,7 +5242,7 @@
       <c r="AW21" s="37"/>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A22" s="100" t="s">
+      <c r="A22" s="91" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -5275,7 +5299,7 @@
       <c r="AW22" s="39"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A23" s="101"/>
+      <c r="A23" s="92"/>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
@@ -5382,7 +5406,7 @@
       <c r="AW23" s="35"/>
     </row>
     <row r="24" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="102"/>
+      <c r="A24" s="93"/>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
@@ -5435,7 +5459,7 @@
       <c r="AW24" s="37"/>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A25" s="100" t="s">
+      <c r="A25" s="91" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -5492,7 +5516,7 @@
       <c r="AW25" s="39"/>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A26" s="101"/>
+      <c r="A26" s="92"/>
       <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
@@ -5545,7 +5569,7 @@
       <c r="AW26" s="76"/>
     </row>
     <row r="27" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="102"/>
+      <c r="A27" s="93"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -5598,7 +5622,7 @@
       <c r="AW27" s="37"/>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="91" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -5655,7 +5679,7 @@
       <c r="AW28" s="39"/>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A29" s="101"/>
+      <c r="A29" s="92"/>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
@@ -5708,7 +5732,7 @@
       <c r="AW29" s="35"/>
     </row>
     <row r="30" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="102"/>
+      <c r="A30" s="93"/>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
@@ -5761,7 +5785,7 @@
       <c r="AW30" s="37"/>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A31" s="100" t="s">
+      <c r="A31" s="91" t="s">
         <v>21</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -5818,7 +5842,7 @@
       <c r="AW31" s="39"/>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A32" s="101"/>
+      <c r="A32" s="92"/>
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -5871,7 +5895,7 @@
       <c r="AW32" s="35"/>
     </row>
     <row r="33" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="103"/>
+      <c r="A33" s="94"/>
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
@@ -5956,6 +5980,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AL1:AP1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="X1:AB1"/>
+    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
@@ -5969,13 +6000,6 @@
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="AL1:AP1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="AE1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6003,26 +6027,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="508407daaf082c5381f5a7b4d9841321">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d41ad40f3ea4d0f4b8e18c6becc727c2" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -6257,32 +6261,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D3E6B6-1954-499D-AE9A-4487E5EEA9C5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6299,4 +6298,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="476" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D2A1CF1-0BB7-4312-A42E-8559B70FEBDB}"/>
+  <xr:revisionPtr revIDLastSave="482" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{19F9E65D-69CA-4424-A2B8-6888C025342A}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -840,7 +840,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1072,6 +1072,51 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1101,45 +1146,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3798,77 +3804,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="104">
-        <v>1</v>
-      </c>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="106"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="100">
+        <v>1</v>
+      </c>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="102"/>
       <c r="H1" s="54"/>
       <c r="I1" s="55"/>
-      <c r="J1" s="104">
+      <c r="J1" s="100">
         <v>2</v>
       </c>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="106"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="102"/>
       <c r="O1" s="54"/>
       <c r="P1" s="55"/>
-      <c r="Q1" s="104">
+      <c r="Q1" s="100">
         <v>3</v>
       </c>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="106"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="102"/>
       <c r="V1" s="54"/>
       <c r="W1" s="55"/>
-      <c r="X1" s="104">
+      <c r="X1" s="100">
         <v>4</v>
       </c>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="105"/>
-      <c r="AA1" s="105"/>
-      <c r="AB1" s="106"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="102"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="55"/>
-      <c r="AE1" s="107">
+      <c r="AE1" s="103">
         <v>5</v>
       </c>
-      <c r="AF1" s="108"/>
-      <c r="AG1" s="108"/>
-      <c r="AH1" s="108"/>
-      <c r="AI1" s="109"/>
+      <c r="AF1" s="104"/>
+      <c r="AG1" s="104"/>
+      <c r="AH1" s="104"/>
+      <c r="AI1" s="105"/>
       <c r="AJ1" s="63"/>
       <c r="AK1" s="64"/>
-      <c r="AL1" s="101">
+      <c r="AL1" s="97">
         <v>6</v>
       </c>
-      <c r="AM1" s="102"/>
-      <c r="AN1" s="102"/>
-      <c r="AO1" s="102"/>
-      <c r="AP1" s="103"/>
+      <c r="AM1" s="98"/>
+      <c r="AN1" s="98"/>
+      <c r="AO1" s="98"/>
+      <c r="AP1" s="99"/>
       <c r="AQ1" s="63"/>
       <c r="AR1" s="64"/>
-      <c r="AS1" s="101">
+      <c r="AS1" s="97">
         <v>7</v>
       </c>
-      <c r="AT1" s="102"/>
-      <c r="AU1" s="102"/>
-      <c r="AV1" s="102"/>
-      <c r="AW1" s="103"/>
+      <c r="AT1" s="98"/>
+      <c r="AU1" s="98"/>
+      <c r="AV1" s="98"/>
+      <c r="AW1" s="99"/>
     </row>
     <row r="2" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="98"/>
+      <c r="B2" s="113"/>
       <c r="C2" s="6">
         <v>1</v>
       </c>
@@ -3988,10 +3994,10 @@
       </c>
     </row>
     <row r="3" spans="1:52" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="99" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="100"/>
+      <c r="A3" s="114" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="115"/>
       <c r="C3" s="49">
         <v>45887</v>
       </c>
@@ -4135,7 +4141,7 @@
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="107" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4190,7 +4196,7 @@
       <c r="AW4" s="39"/>
     </row>
     <row r="5" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="92"/>
+      <c r="A5" s="107"/>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4249,14 +4255,14 @@
       <c r="AW5" s="35"/>
     </row>
     <row r="6" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="93"/>
+      <c r="A6" s="108"/>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="110"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="21"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="96"/>
       <c r="G6" s="21"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
@@ -4308,7 +4314,7 @@
       </c>
     </row>
     <row r="7" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="106" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4372,7 +4378,7 @@
       </c>
     </row>
     <row r="8" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="92"/>
+      <c r="A8" s="107"/>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
@@ -4440,14 +4446,14 @@
       </c>
     </row>
     <row r="9" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="93"/>
+      <c r="A9" s="108"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="19"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="20"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="95"/>
       <c r="G9" s="20"/>
       <c r="H9" s="46"/>
       <c r="I9" s="46"/>
@@ -4500,7 +4506,7 @@
       </c>
     </row>
     <row r="10" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91" t="s">
+      <c r="A10" s="106" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4517,12 +4523,11 @@
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
-      <c r="N10" s="72" t="s">
-        <v>14</v>
-      </c>
       <c r="O10" s="40"/>
       <c r="P10" s="40"/>
-      <c r="Q10" s="13"/>
+      <c r="Q10" s="72" t="s">
+        <v>14</v>
+      </c>
       <c r="R10" s="13"/>
       <c r="S10" s="13"/>
       <c r="T10" s="13"/>
@@ -4564,7 +4569,7 @@
       </c>
     </row>
     <row r="11" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="92"/>
+      <c r="A11" s="107"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -4630,7 +4635,7 @@
       </c>
     </row>
     <row r="12" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="93"/>
+      <c r="A12" s="108"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -4690,7 +4695,7 @@
       </c>
     </row>
     <row r="13" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="91" t="s">
+      <c r="A13" s="106" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -4752,7 +4757,7 @@
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A14" s="92"/>
+      <c r="A14" s="107"/>
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
@@ -4809,7 +4814,7 @@
       <c r="AW14" s="35"/>
     </row>
     <row r="15" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="93"/>
+      <c r="A15" s="108"/>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
@@ -4862,7 +4867,7 @@
       <c r="AW15" s="37"/>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="106" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4917,7 +4922,7 @@
       <c r="AW16" s="39"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A17" s="92"/>
+      <c r="A17" s="107"/>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
@@ -5012,7 +5017,7 @@
       <c r="AW17" s="35"/>
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="93"/>
+      <c r="A18" s="108"/>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
@@ -5065,7 +5070,7 @@
       <c r="AW18" s="37"/>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A19" s="91" t="s">
+      <c r="A19" s="106" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -5120,7 +5125,7 @@
       <c r="AW19" s="39"/>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A20" s="92"/>
+      <c r="A20" s="107"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
@@ -5189,7 +5194,7 @@
       <c r="AW20" s="35"/>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="93"/>
+      <c r="A21" s="108"/>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
@@ -5242,7 +5247,7 @@
       <c r="AW21" s="37"/>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="106" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -5299,7 +5304,7 @@
       <c r="AW22" s="39"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A23" s="92"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
@@ -5406,7 +5411,7 @@
       <c r="AW23" s="35"/>
     </row>
     <row r="24" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="93"/>
+      <c r="A24" s="108"/>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
@@ -5459,7 +5464,7 @@
       <c r="AW24" s="37"/>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A25" s="91" t="s">
+      <c r="A25" s="106" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -5516,7 +5521,7 @@
       <c r="AW25" s="39"/>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A26" s="92"/>
+      <c r="A26" s="107"/>
       <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
@@ -5569,7 +5574,7 @@
       <c r="AW26" s="76"/>
     </row>
     <row r="27" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="93"/>
+      <c r="A27" s="108"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -5622,7 +5627,7 @@
       <c r="AW27" s="37"/>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A28" s="91" t="s">
+      <c r="A28" s="106" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -5679,7 +5684,7 @@
       <c r="AW28" s="39"/>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A29" s="92"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
@@ -5732,7 +5737,7 @@
       <c r="AW29" s="35"/>
     </row>
     <row r="30" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="93"/>
+      <c r="A30" s="108"/>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
@@ -5785,7 +5790,7 @@
       <c r="AW30" s="37"/>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A31" s="91" t="s">
+      <c r="A31" s="106" t="s">
         <v>21</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -5842,7 +5847,7 @@
       <c r="AW31" s="39"/>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A32" s="92"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -5895,7 +5900,7 @@
       <c r="AW32" s="35"/>
     </row>
     <row r="33" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="94"/>
+      <c r="A33" s="109"/>
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
@@ -5980,13 +5985,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AL1:AP1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
@@ -6000,6 +5998,13 @@
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A19:A21"/>
+    <mergeCell ref="AL1:AP1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="X1:AB1"/>
+    <mergeCell ref="AE1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6027,6 +6032,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="508407daaf082c5381f5a7b4d9841321">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d41ad40f3ea4d0f4b8e18c6becc727c2" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -6261,15 +6275,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6282,6 +6287,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D3E6B6-1954-499D-AE9A-4487E5EEA9C5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6296,14 +6309,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="482" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{19F9E65D-69CA-4424-A2B8-6888C025342A}"/>
+  <xr:revisionPtr revIDLastSave="489" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{583866E7-B6A1-41D4-A91F-4F3779852F9B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -840,7 +840,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1090,6 +1090,36 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1117,35 +1147,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3804,77 +3810,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="100">
-        <v>1</v>
-      </c>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="102"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="110">
+        <v>1</v>
+      </c>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="112"/>
       <c r="H1" s="54"/>
       <c r="I1" s="55"/>
-      <c r="J1" s="100">
+      <c r="J1" s="110">
         <v>2</v>
       </c>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="102"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="112"/>
       <c r="O1" s="54"/>
       <c r="P1" s="55"/>
-      <c r="Q1" s="100">
+      <c r="Q1" s="110">
         <v>3</v>
       </c>
-      <c r="R1" s="101"/>
-      <c r="S1" s="101"/>
-      <c r="T1" s="101"/>
-      <c r="U1" s="102"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="112"/>
       <c r="V1" s="54"/>
       <c r="W1" s="55"/>
-      <c r="X1" s="100">
+      <c r="X1" s="110">
         <v>4</v>
       </c>
-      <c r="Y1" s="101"/>
-      <c r="Z1" s="101"/>
-      <c r="AA1" s="101"/>
-      <c r="AB1" s="102"/>
+      <c r="Y1" s="111"/>
+      <c r="Z1" s="111"/>
+      <c r="AA1" s="111"/>
+      <c r="AB1" s="112"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="55"/>
-      <c r="AE1" s="103">
+      <c r="AE1" s="113">
         <v>5</v>
       </c>
-      <c r="AF1" s="104"/>
-      <c r="AG1" s="104"/>
-      <c r="AH1" s="104"/>
-      <c r="AI1" s="105"/>
+      <c r="AF1" s="114"/>
+      <c r="AG1" s="114"/>
+      <c r="AH1" s="114"/>
+      <c r="AI1" s="115"/>
       <c r="AJ1" s="63"/>
       <c r="AK1" s="64"/>
-      <c r="AL1" s="97">
+      <c r="AL1" s="107">
         <v>6</v>
       </c>
-      <c r="AM1" s="98"/>
-      <c r="AN1" s="98"/>
-      <c r="AO1" s="98"/>
-      <c r="AP1" s="99"/>
+      <c r="AM1" s="108"/>
+      <c r="AN1" s="108"/>
+      <c r="AO1" s="108"/>
+      <c r="AP1" s="109"/>
       <c r="AQ1" s="63"/>
       <c r="AR1" s="64"/>
-      <c r="AS1" s="97">
+      <c r="AS1" s="107">
         <v>7</v>
       </c>
-      <c r="AT1" s="98"/>
-      <c r="AU1" s="98"/>
-      <c r="AV1" s="98"/>
-      <c r="AW1" s="99"/>
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="109"/>
     </row>
     <row r="2" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="113"/>
+      <c r="B2" s="104"/>
       <c r="C2" s="6">
         <v>1</v>
       </c>
@@ -3994,10 +4000,10 @@
       </c>
     </row>
     <row r="3" spans="1:52" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="114" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="115"/>
+      <c r="A3" s="105" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="106"/>
       <c r="C3" s="49">
         <v>45887</v>
       </c>
@@ -4141,7 +4147,7 @@
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A4" s="107" t="s">
+      <c r="A4" s="98" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4196,7 +4202,7 @@
       <c r="AW4" s="39"/>
     </row>
     <row r="5" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="107"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4255,7 +4261,7 @@
       <c r="AW5" s="35"/>
     </row>
     <row r="6" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="108"/>
+      <c r="A6" s="99"/>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
@@ -4314,7 +4320,7 @@
       </c>
     </row>
     <row r="7" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="106" t="s">
+      <c r="A7" s="97" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4378,7 +4384,7 @@
       </c>
     </row>
     <row r="8" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="107"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
@@ -4398,7 +4404,7 @@
       <c r="J8" s="80">
         <v>1</v>
       </c>
-      <c r="K8" s="27"/>
+      <c r="K8" s="117"/>
       <c r="L8" s="27"/>
       <c r="M8" s="27"/>
       <c r="N8" s="27"/>
@@ -4446,7 +4452,7 @@
       </c>
     </row>
     <row r="9" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="108"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -4454,11 +4460,11 @@
       <c r="D9" s="93"/>
       <c r="E9" s="93"/>
       <c r="F9" s="95"/>
-      <c r="G9" s="20"/>
+      <c r="G9" s="95"/>
       <c r="H9" s="46"/>
       <c r="I9" s="46"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="21"/>
+      <c r="J9" s="93"/>
+      <c r="K9" s="116"/>
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
       <c r="N9" s="21"/>
@@ -4506,7 +4512,7 @@
       </c>
     </row>
     <row r="10" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="106" t="s">
+      <c r="A10" s="97" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4569,7 +4575,7 @@
       </c>
     </row>
     <row r="11" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="107"/>
+      <c r="A11" s="98"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -4635,7 +4641,7 @@
       </c>
     </row>
     <row r="12" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="108"/>
+      <c r="A12" s="99"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -4695,7 +4701,7 @@
       </c>
     </row>
     <row r="13" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="97" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -4757,7 +4763,7 @@
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A14" s="107"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
@@ -4814,7 +4820,7 @@
       <c r="AW14" s="35"/>
     </row>
     <row r="15" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="108"/>
+      <c r="A15" s="99"/>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
@@ -4867,7 +4873,7 @@
       <c r="AW15" s="37"/>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A16" s="106" t="s">
+      <c r="A16" s="97" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4922,7 +4928,7 @@
       <c r="AW16" s="39"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A17" s="107"/>
+      <c r="A17" s="98"/>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
@@ -5017,7 +5023,7 @@
       <c r="AW17" s="35"/>
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="108"/>
+      <c r="A18" s="99"/>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
@@ -5070,7 +5076,7 @@
       <c r="AW18" s="37"/>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A19" s="106" t="s">
+      <c r="A19" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -5125,7 +5131,7 @@
       <c r="AW19" s="39"/>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A20" s="107"/>
+      <c r="A20" s="98"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
@@ -5194,7 +5200,7 @@
       <c r="AW20" s="35"/>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="108"/>
+      <c r="A21" s="99"/>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
@@ -5247,7 +5253,7 @@
       <c r="AW21" s="37"/>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A22" s="106" t="s">
+      <c r="A22" s="97" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -5304,7 +5310,7 @@
       <c r="AW22" s="39"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A23" s="107"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
@@ -5411,7 +5417,7 @@
       <c r="AW23" s="35"/>
     </row>
     <row r="24" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="108"/>
+      <c r="A24" s="99"/>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
@@ -5464,7 +5470,7 @@
       <c r="AW24" s="37"/>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A25" s="106" t="s">
+      <c r="A25" s="97" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -5521,7 +5527,7 @@
       <c r="AW25" s="39"/>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A26" s="107"/>
+      <c r="A26" s="98"/>
       <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
@@ -5574,7 +5580,7 @@
       <c r="AW26" s="76"/>
     </row>
     <row r="27" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="108"/>
+      <c r="A27" s="99"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -5627,7 +5633,7 @@
       <c r="AW27" s="37"/>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="97" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -5684,7 +5690,7 @@
       <c r="AW28" s="39"/>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A29" s="107"/>
+      <c r="A29" s="98"/>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
@@ -5737,7 +5743,7 @@
       <c r="AW29" s="35"/>
     </row>
     <row r="30" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="108"/>
+      <c r="A30" s="99"/>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
@@ -5790,7 +5796,7 @@
       <c r="AW30" s="37"/>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A31" s="106" t="s">
+      <c r="A31" s="97" t="s">
         <v>21</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -5847,7 +5853,7 @@
       <c r="AW31" s="39"/>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A32" s="107"/>
+      <c r="A32" s="98"/>
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -5900,7 +5906,7 @@
       <c r="AW32" s="35"/>
     </row>
     <row r="33" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="109"/>
+      <c r="A33" s="100"/>
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
@@ -5985,6 +5991,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AL1:AP1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="X1:AB1"/>
+    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
@@ -5998,13 +6011,6 @@
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="AL1:AP1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="AE1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6032,12 +6038,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6276,20 +6284,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6314,18 +6329,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="489" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{583866E7-B6A1-41D4-A91F-4F3779852F9B}"/>
+  <xr:revisionPtr revIDLastSave="505" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5F6DB47-6E14-4DE0-9B2D-D12C64557495}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -190,7 +190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -293,6 +293,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="43">
     <border>
@@ -840,7 +852,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -897,9 +909,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1090,6 +1099,39 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1120,37 +1162,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1568,13 +1583,13 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>21</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>8</c:v>
@@ -3810,77 +3825,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="110">
-        <v>1</v>
-      </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="110">
+      <c r="B1" s="112"/>
+      <c r="C1" s="101">
+        <v>1</v>
+      </c>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="101">
         <v>2</v>
       </c>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="110">
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="101">
         <v>3</v>
       </c>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="54"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="110">
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="103"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="101">
         <v>4</v>
       </c>
-      <c r="Y1" s="111"/>
-      <c r="Z1" s="111"/>
-      <c r="AA1" s="111"/>
-      <c r="AB1" s="112"/>
-      <c r="AC1" s="54"/>
-      <c r="AD1" s="55"/>
-      <c r="AE1" s="113">
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="103"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="54"/>
+      <c r="AE1" s="104">
         <v>5</v>
       </c>
-      <c r="AF1" s="114"/>
-      <c r="AG1" s="114"/>
-      <c r="AH1" s="114"/>
-      <c r="AI1" s="115"/>
-      <c r="AJ1" s="63"/>
-      <c r="AK1" s="64"/>
-      <c r="AL1" s="107">
+      <c r="AF1" s="105"/>
+      <c r="AG1" s="105"/>
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="106"/>
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="98">
         <v>6</v>
       </c>
-      <c r="AM1" s="108"/>
-      <c r="AN1" s="108"/>
-      <c r="AO1" s="108"/>
-      <c r="AP1" s="109"/>
-      <c r="AQ1" s="63"/>
-      <c r="AR1" s="64"/>
-      <c r="AS1" s="107">
+      <c r="AM1" s="99"/>
+      <c r="AN1" s="99"/>
+      <c r="AO1" s="99"/>
+      <c r="AP1" s="100"/>
+      <c r="AQ1" s="62"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="98">
         <v>7</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="109"/>
+      <c r="AT1" s="99"/>
+      <c r="AU1" s="99"/>
+      <c r="AV1" s="99"/>
+      <c r="AW1" s="100"/>
     </row>
     <row r="2" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="104"/>
+      <c r="B2" s="114"/>
       <c r="C2" s="6">
         <v>1</v>
       </c>
@@ -3896,8 +3911,8 @@
       <c r="G2" s="11">
         <v>5</v>
       </c>
-      <c r="H2" s="56"/>
-      <c r="I2" s="57"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="56"/>
       <c r="J2" s="6">
         <v>1</v>
       </c>
@@ -3913,8 +3928,8 @@
       <c r="N2" s="11">
         <v>5</v>
       </c>
-      <c r="O2" s="56"/>
-      <c r="P2" s="57"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="56"/>
       <c r="Q2" s="6">
         <v>1</v>
       </c>
@@ -3930,8 +3945,8 @@
       <c r="U2" s="11">
         <v>5</v>
       </c>
-      <c r="V2" s="56"/>
-      <c r="W2" s="57"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="56"/>
       <c r="X2" s="6">
         <v>1</v>
       </c>
@@ -3947,8 +3962,8 @@
       <c r="AB2" s="11">
         <v>5</v>
       </c>
-      <c r="AC2" s="56"/>
-      <c r="AD2" s="57"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="56"/>
       <c r="AE2" s="6">
         <v>1</v>
       </c>
@@ -3964,8 +3979,8 @@
       <c r="AI2" s="11">
         <v>5</v>
       </c>
-      <c r="AJ2" s="65"/>
-      <c r="AK2" s="66"/>
+      <c r="AJ2" s="64"/>
+      <c r="AK2" s="65"/>
       <c r="AL2" s="6">
         <v>1</v>
       </c>
@@ -3981,8 +3996,8 @@
       <c r="AP2" s="11">
         <v>5</v>
       </c>
-      <c r="AQ2" s="65"/>
-      <c r="AR2" s="66"/>
+      <c r="AQ2" s="64"/>
+      <c r="AR2" s="65"/>
       <c r="AS2" s="6">
         <v>1</v>
       </c>
@@ -4000,154 +4015,154 @@
       </c>
     </row>
     <row r="3" spans="1:52" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="105" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="49">
+      <c r="A3" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="116"/>
+      <c r="C3" s="48">
         <v>45887</v>
       </c>
-      <c r="D3" s="50">
+      <c r="D3" s="49">
         <v>45888</v>
       </c>
-      <c r="E3" s="50">
+      <c r="E3" s="49">
         <v>45889</v>
       </c>
-      <c r="F3" s="50">
+      <c r="F3" s="49">
         <v>45890</v>
       </c>
-      <c r="G3" s="51">
+      <c r="G3" s="50">
         <v>45891</v>
       </c>
-      <c r="H3" s="52">
+      <c r="H3" s="51">
         <v>45892</v>
       </c>
-      <c r="I3" s="53">
+      <c r="I3" s="52">
         <v>45893</v>
       </c>
-      <c r="J3" s="49">
+      <c r="J3" s="48">
         <v>45894</v>
       </c>
-      <c r="K3" s="50">
+      <c r="K3" s="49">
         <v>45895</v>
       </c>
-      <c r="L3" s="50">
+      <c r="L3" s="49">
         <v>45896</v>
       </c>
-      <c r="M3" s="50">
+      <c r="M3" s="49">
         <v>45897</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="50">
         <v>45898</v>
       </c>
-      <c r="O3" s="52">
+      <c r="O3" s="51">
         <v>45899</v>
       </c>
-      <c r="P3" s="53">
+      <c r="P3" s="52">
         <v>45900</v>
       </c>
-      <c r="Q3" s="49">
+      <c r="Q3" s="48">
         <v>45901</v>
       </c>
-      <c r="R3" s="50">
+      <c r="R3" s="49">
         <v>45902</v>
       </c>
-      <c r="S3" s="50">
+      <c r="S3" s="49">
         <v>45903</v>
       </c>
-      <c r="T3" s="50">
+      <c r="T3" s="49">
         <v>45904</v>
       </c>
-      <c r="U3" s="51">
+      <c r="U3" s="50">
         <v>45905</v>
       </c>
-      <c r="V3" s="52">
+      <c r="V3" s="51">
         <v>45906</v>
       </c>
-      <c r="W3" s="53">
+      <c r="W3" s="52">
         <v>45907</v>
       </c>
-      <c r="X3" s="49">
+      <c r="X3" s="48">
         <v>45908</v>
       </c>
-      <c r="Y3" s="50">
+      <c r="Y3" s="49">
         <v>45909</v>
       </c>
-      <c r="Z3" s="50">
+      <c r="Z3" s="49">
         <v>45910</v>
       </c>
-      <c r="AA3" s="50">
+      <c r="AA3" s="49">
         <v>45911</v>
       </c>
-      <c r="AB3" s="51">
+      <c r="AB3" s="50">
         <v>45912</v>
       </c>
-      <c r="AC3" s="52">
+      <c r="AC3" s="51">
         <v>45913</v>
       </c>
-      <c r="AD3" s="53">
+      <c r="AD3" s="52">
         <v>45914</v>
       </c>
-      <c r="AE3" s="49">
+      <c r="AE3" s="48">
         <v>45915</v>
       </c>
-      <c r="AF3" s="50">
+      <c r="AF3" s="49">
         <v>45916</v>
       </c>
-      <c r="AG3" s="50">
+      <c r="AG3" s="49">
         <v>45917</v>
       </c>
-      <c r="AH3" s="50">
+      <c r="AH3" s="49">
         <v>45918</v>
       </c>
-      <c r="AI3" s="51">
+      <c r="AI3" s="50">
         <v>45919</v>
       </c>
-      <c r="AJ3" s="52">
+      <c r="AJ3" s="51">
         <v>45920</v>
       </c>
-      <c r="AK3" s="53">
+      <c r="AK3" s="52">
         <v>45921</v>
       </c>
-      <c r="AL3" s="49">
+      <c r="AL3" s="48">
         <v>45922</v>
       </c>
-      <c r="AM3" s="50">
+      <c r="AM3" s="49">
         <v>45923</v>
       </c>
-      <c r="AN3" s="50">
+      <c r="AN3" s="49">
         <v>45924</v>
       </c>
-      <c r="AO3" s="50">
+      <c r="AO3" s="49">
         <v>45925</v>
       </c>
-      <c r="AP3" s="51">
+      <c r="AP3" s="50">
         <v>45926</v>
       </c>
-      <c r="AQ3" s="52">
+      <c r="AQ3" s="51">
         <v>45927</v>
       </c>
-      <c r="AR3" s="53">
+      <c r="AR3" s="52">
         <v>45928</v>
       </c>
-      <c r="AS3" s="49">
+      <c r="AS3" s="48">
         <v>45929</v>
       </c>
-      <c r="AT3" s="50">
+      <c r="AT3" s="49">
         <v>45930</v>
       </c>
-      <c r="AU3" s="50">
+      <c r="AU3" s="49">
         <v>45931</v>
       </c>
-      <c r="AV3" s="50">
+      <c r="AV3" s="49">
         <v>45932</v>
       </c>
-      <c r="AW3" s="51">
+      <c r="AW3" s="50">
         <v>45933</v>
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="108" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4158,169 +4173,169 @@
       <c r="E4" s="16"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
       <c r="L4" s="16"/>
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
       <c r="Q4" s="16"/>
       <c r="R4" s="16"/>
       <c r="S4" s="16"/>
       <c r="T4" s="16"/>
       <c r="U4" s="16"/>
-      <c r="V4" s="42"/>
-      <c r="W4" s="60"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="59"/>
       <c r="X4" s="16"/>
       <c r="Y4" s="16"/>
       <c r="Z4" s="18"/>
       <c r="AA4" s="16"/>
       <c r="AB4" s="16"/>
-      <c r="AC4" s="42"/>
-      <c r="AD4" s="60"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="59"/>
       <c r="AE4" s="16"/>
       <c r="AF4" s="16"/>
       <c r="AG4" s="16"/>
       <c r="AH4" s="16"/>
       <c r="AI4" s="17"/>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="67"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="67"/>
-      <c r="AR4" s="67"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="39"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="37"/>
+      <c r="AM4" s="37"/>
+      <c r="AN4" s="37"/>
+      <c r="AO4" s="37"/>
+      <c r="AP4" s="37"/>
+      <c r="AQ4" s="66"/>
+      <c r="AR4" s="66"/>
+      <c r="AS4" s="37"/>
+      <c r="AT4" s="37"/>
+      <c r="AU4" s="37"/>
+      <c r="AV4" s="37"/>
+      <c r="AW4" s="38"/>
     </row>
     <row r="5" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="98"/>
+      <c r="A5" s="108"/>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="78">
-        <v>1</v>
-      </c>
-      <c r="D5" s="79">
-        <v>1</v>
-      </c>
-      <c r="E5" s="79">
+      <c r="C5" s="77">
+        <v>1</v>
+      </c>
+      <c r="D5" s="78">
+        <v>1</v>
+      </c>
+      <c r="E5" s="78">
         <v>1</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
       <c r="L5" s="16"/>
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
       <c r="U5" s="16"/>
-      <c r="V5" s="42"/>
-      <c r="W5" s="60"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="59"/>
       <c r="X5" s="16"/>
       <c r="Y5" s="16"/>
       <c r="Z5" s="18"/>
       <c r="AA5" s="16"/>
       <c r="AB5" s="16"/>
-      <c r="AC5" s="42"/>
-      <c r="AD5" s="60"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="59"/>
       <c r="AE5" s="16"/>
       <c r="AF5" s="16"/>
       <c r="AG5" s="16"/>
       <c r="AH5" s="16"/>
       <c r="AI5" s="17"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="34"/>
-      <c r="AM5" s="34"/>
-      <c r="AN5" s="34"/>
-      <c r="AO5" s="34"/>
-      <c r="AP5" s="34"/>
-      <c r="AQ5" s="68"/>
-      <c r="AR5" s="68"/>
-      <c r="AS5" s="34"/>
-      <c r="AT5" s="34"/>
-      <c r="AU5" s="34"/>
-      <c r="AV5" s="34"/>
-      <c r="AW5" s="35"/>
+      <c r="AJ5" s="67"/>
+      <c r="AK5" s="67"/>
+      <c r="AL5" s="33"/>
+      <c r="AM5" s="33"/>
+      <c r="AN5" s="33"/>
+      <c r="AO5" s="33"/>
+      <c r="AP5" s="33"/>
+      <c r="AQ5" s="67"/>
+      <c r="AR5" s="67"/>
+      <c r="AS5" s="33"/>
+      <c r="AT5" s="33"/>
+      <c r="AU5" s="33"/>
+      <c r="AV5" s="33"/>
+      <c r="AW5" s="34"/>
     </row>
     <row r="6" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="99"/>
+      <c r="A6" s="109"/>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="91"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="21"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="59"/>
-      <c r="X6" s="21"/>
-      <c r="Y6" s="21"/>
-      <c r="Z6" s="23"/>
-      <c r="AA6" s="21"/>
-      <c r="AB6" s="21"/>
-      <c r="AC6" s="41"/>
-      <c r="AD6" s="59"/>
-      <c r="AE6" s="21"/>
-      <c r="AF6" s="21"/>
-      <c r="AG6" s="21"/>
-      <c r="AH6" s="21"/>
-      <c r="AI6" s="22"/>
-      <c r="AJ6" s="69"/>
-      <c r="AK6" s="69"/>
-      <c r="AL6" s="36"/>
-      <c r="AM6" s="36"/>
-      <c r="AN6" s="36"/>
-      <c r="AO6" s="36"/>
-      <c r="AP6" s="36"/>
-      <c r="AQ6" s="69"/>
-      <c r="AR6" s="69"/>
-      <c r="AS6" s="36"/>
-      <c r="AT6" s="36"/>
-      <c r="AU6" s="36"/>
-      <c r="AV6" s="36"/>
-      <c r="AW6" s="37"/>
-      <c r="AY6" s="77" t="s">
+      <c r="C6" s="90"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="40"/>
+      <c r="W6" s="58"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="58"/>
+      <c r="AE6" s="20"/>
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="20"/>
+      <c r="AI6" s="21"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="35"/>
+      <c r="AM6" s="35"/>
+      <c r="AN6" s="35"/>
+      <c r="AO6" s="35"/>
+      <c r="AP6" s="35"/>
+      <c r="AQ6" s="68"/>
+      <c r="AR6" s="68"/>
+      <c r="AS6" s="35"/>
+      <c r="AT6" s="35"/>
+      <c r="AU6" s="35"/>
+      <c r="AV6" s="35"/>
+      <c r="AW6" s="36"/>
+      <c r="AY6" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="AZ6" s="77" t="s">
+      <c r="AZ6" s="76" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="97" t="s">
+      <c r="A7" s="107" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4328,191 +4343,191 @@
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="13"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="72" t="s">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="71" t="s">
         <v>14</v>
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
       <c r="S7" s="13"/>
       <c r="T7" s="13"/>
       <c r="U7" s="13"/>
-      <c r="V7" s="40"/>
-      <c r="W7" s="55"/>
+      <c r="V7" s="39"/>
+      <c r="W7" s="54"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="13"/>
       <c r="Z7" s="15"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="13"/>
-      <c r="AC7" s="40"/>
-      <c r="AD7" s="55"/>
+      <c r="AC7" s="39"/>
+      <c r="AD7" s="54"/>
       <c r="AE7" s="13"/>
       <c r="AF7" s="13"/>
       <c r="AG7" s="13"/>
       <c r="AH7" s="13"/>
       <c r="AI7" s="14"/>
-      <c r="AJ7" s="67"/>
-      <c r="AK7" s="67"/>
-      <c r="AL7" s="38"/>
-      <c r="AM7" s="38"/>
-      <c r="AN7" s="38"/>
-      <c r="AO7" s="38"/>
-      <c r="AP7" s="38"/>
-      <c r="AQ7" s="67"/>
-      <c r="AR7" s="67"/>
-      <c r="AS7" s="38"/>
-      <c r="AT7" s="38"/>
-      <c r="AU7" s="38"/>
-      <c r="AV7" s="38"/>
-      <c r="AW7" s="39"/>
-      <c r="AY7" s="77" t="s">
+      <c r="AJ7" s="66"/>
+      <c r="AK7" s="66"/>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="37"/>
+      <c r="AN7" s="37"/>
+      <c r="AO7" s="37"/>
+      <c r="AP7" s="37"/>
+      <c r="AQ7" s="66"/>
+      <c r="AR7" s="66"/>
+      <c r="AS7" s="37"/>
+      <c r="AT7" s="37"/>
+      <c r="AU7" s="37"/>
+      <c r="AV7" s="37"/>
+      <c r="AW7" s="38"/>
+      <c r="AY7" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="AZ7" s="77">
+      <c r="AZ7" s="76">
         <f>SUM(C5:AW5)</f>
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="98"/>
+      <c r="A8" s="108"/>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="80">
-        <v>1</v>
-      </c>
-      <c r="F8" s="80">
-        <v>1</v>
-      </c>
-      <c r="G8" s="80">
-        <v>1</v>
-      </c>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="80">
-        <v>1</v>
-      </c>
-      <c r="K8" s="117"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-      <c r="V8" s="47"/>
-      <c r="W8" s="58"/>
-      <c r="X8" s="26"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="29"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="26"/>
-      <c r="AC8" s="47"/>
-      <c r="AD8" s="58"/>
-      <c r="AE8" s="26"/>
-      <c r="AF8" s="26"/>
-      <c r="AG8" s="26"/>
-      <c r="AH8" s="26"/>
-      <c r="AI8" s="28"/>
-      <c r="AJ8" s="68"/>
-      <c r="AK8" s="68"/>
-      <c r="AL8" s="34"/>
-      <c r="AM8" s="34"/>
-      <c r="AN8" s="34"/>
-      <c r="AO8" s="34"/>
-      <c r="AP8" s="34"/>
-      <c r="AQ8" s="68"/>
-      <c r="AR8" s="68"/>
-      <c r="AS8" s="34"/>
-      <c r="AT8" s="34"/>
-      <c r="AU8" s="34"/>
-      <c r="AV8" s="34"/>
-      <c r="AW8" s="35"/>
-      <c r="AY8" s="77" t="s">
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="79">
+        <v>1</v>
+      </c>
+      <c r="F8" s="79">
+        <v>1</v>
+      </c>
+      <c r="G8" s="79">
+        <v>1</v>
+      </c>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="79">
+        <v>1</v>
+      </c>
+      <c r="K8" s="97"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="57"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="46"/>
+      <c r="AD8" s="57"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="25"/>
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="27"/>
+      <c r="AJ8" s="67"/>
+      <c r="AK8" s="67"/>
+      <c r="AL8" s="33"/>
+      <c r="AM8" s="33"/>
+      <c r="AN8" s="33"/>
+      <c r="AO8" s="33"/>
+      <c r="AP8" s="33"/>
+      <c r="AQ8" s="67"/>
+      <c r="AR8" s="67"/>
+      <c r="AS8" s="33"/>
+      <c r="AT8" s="33"/>
+      <c r="AU8" s="33"/>
+      <c r="AV8" s="33"/>
+      <c r="AW8" s="34"/>
+      <c r="AY8" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="AZ8" s="77">
+      <c r="AZ8" s="76">
         <f>SUM(C8:AW8)</f>
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="99"/>
+      <c r="A9" s="109"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="19"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="93"/>
-      <c r="K9" s="116"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="21"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="21"/>
-      <c r="Z9" s="23"/>
-      <c r="AA9" s="21"/>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="41"/>
-      <c r="AD9" s="59"/>
-      <c r="AE9" s="21"/>
-      <c r="AF9" s="21"/>
-      <c r="AG9" s="21"/>
-      <c r="AH9" s="21"/>
-      <c r="AI9" s="22"/>
-      <c r="AJ9" s="69"/>
-      <c r="AK9" s="69"/>
-      <c r="AL9" s="36"/>
-      <c r="AM9" s="36"/>
-      <c r="AN9" s="36"/>
-      <c r="AO9" s="36"/>
-      <c r="AP9" s="36"/>
-      <c r="AQ9" s="69"/>
-      <c r="AR9" s="69"/>
-      <c r="AS9" s="36"/>
-      <c r="AT9" s="36"/>
-      <c r="AU9" s="36"/>
-      <c r="AV9" s="36"/>
-      <c r="AW9" s="37"/>
-      <c r="AY9" s="77" t="s">
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="92"/>
+      <c r="M9" s="92"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="58"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
+      <c r="AG9" s="20"/>
+      <c r="AH9" s="20"/>
+      <c r="AI9" s="21"/>
+      <c r="AJ9" s="68"/>
+      <c r="AK9" s="68"/>
+      <c r="AL9" s="35"/>
+      <c r="AM9" s="35"/>
+      <c r="AN9" s="35"/>
+      <c r="AO9" s="35"/>
+      <c r="AP9" s="35"/>
+      <c r="AQ9" s="68"/>
+      <c r="AR9" s="68"/>
+      <c r="AS9" s="35"/>
+      <c r="AT9" s="35"/>
+      <c r="AU9" s="35"/>
+      <c r="AV9" s="35"/>
+      <c r="AW9" s="36"/>
+      <c r="AY9" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="AZ9" s="77">
+      <c r="AZ9" s="76">
         <f>SUM(C11:AW11)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="107" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4523,185 +4538,191 @@
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
       <c r="G10" s="14"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="72" t="s">
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
       <c r="T10" s="13"/>
       <c r="U10" s="13"/>
-      <c r="V10" s="40"/>
-      <c r="W10" s="40"/>
+      <c r="V10" s="39"/>
+      <c r="W10" s="39"/>
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
       <c r="Z10" s="15"/>
       <c r="AA10" s="13"/>
       <c r="AB10" s="13"/>
-      <c r="AC10" s="40"/>
-      <c r="AD10" s="55"/>
+      <c r="AC10" s="39"/>
+      <c r="AD10" s="54"/>
       <c r="AE10" s="13"/>
       <c r="AF10" s="13"/>
       <c r="AG10" s="13"/>
       <c r="AH10" s="13"/>
       <c r="AI10" s="14"/>
-      <c r="AJ10" s="67"/>
-      <c r="AK10" s="67"/>
-      <c r="AL10" s="38"/>
-      <c r="AM10" s="38"/>
-      <c r="AN10" s="38"/>
-      <c r="AO10" s="38"/>
-      <c r="AP10" s="38"/>
-      <c r="AQ10" s="67"/>
-      <c r="AR10" s="67"/>
-      <c r="AS10" s="38"/>
-      <c r="AT10" s="38"/>
-      <c r="AU10" s="38"/>
-      <c r="AV10" s="38"/>
-      <c r="AW10" s="39"/>
-      <c r="AY10" s="77" t="s">
+      <c r="AJ10" s="66"/>
+      <c r="AK10" s="66"/>
+      <c r="AL10" s="37"/>
+      <c r="AM10" s="37"/>
+      <c r="AN10" s="37"/>
+      <c r="AO10" s="37"/>
+      <c r="AP10" s="37"/>
+      <c r="AQ10" s="66"/>
+      <c r="AR10" s="66"/>
+      <c r="AS10" s="37"/>
+      <c r="AT10" s="37"/>
+      <c r="AU10" s="37"/>
+      <c r="AV10" s="37"/>
+      <c r="AW10" s="38"/>
+      <c r="AY10" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="AZ10" s="77">
+      <c r="AZ10" s="76">
         <f>SUM(C14:AW14)</f>
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="98"/>
+      <c r="A11" s="108"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="81">
-        <v>1</v>
-      </c>
-      <c r="M11" s="81">
-        <v>1</v>
-      </c>
-      <c r="N11" s="81">
-        <v>1</v>
-      </c>
-      <c r="O11" s="47"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="26"/>
-      <c r="S11" s="26"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="47"/>
-      <c r="W11" s="47"/>
-      <c r="X11" s="26"/>
-      <c r="Y11" s="26"/>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="26"/>
-      <c r="AB11" s="26"/>
-      <c r="AC11" s="47"/>
-      <c r="AD11" s="58"/>
-      <c r="AE11" s="26"/>
-      <c r="AF11" s="26"/>
-      <c r="AG11" s="26"/>
-      <c r="AH11" s="26"/>
-      <c r="AI11" s="28"/>
-      <c r="AJ11" s="68"/>
-      <c r="AK11" s="68"/>
-      <c r="AL11" s="34"/>
-      <c r="AM11" s="34"/>
-      <c r="AN11" s="34"/>
-      <c r="AO11" s="34"/>
-      <c r="AP11" s="34"/>
-      <c r="AQ11" s="68"/>
-      <c r="AR11" s="68"/>
-      <c r="AS11" s="34"/>
-      <c r="AT11" s="34"/>
-      <c r="AU11" s="34"/>
-      <c r="AV11" s="34"/>
-      <c r="AW11" s="35"/>
-      <c r="AY11" s="77" t="s">
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="80">
+        <v>1</v>
+      </c>
+      <c r="M11" s="80">
+        <v>1</v>
+      </c>
+      <c r="N11" s="80">
+        <v>1</v>
+      </c>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="80">
+        <v>1</v>
+      </c>
+      <c r="R11" s="80">
+        <v>1</v>
+      </c>
+      <c r="S11" s="80">
+        <v>1</v>
+      </c>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="46"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="28"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="57"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="25"/>
+      <c r="AI11" s="27"/>
+      <c r="AJ11" s="67"/>
+      <c r="AK11" s="67"/>
+      <c r="AL11" s="33"/>
+      <c r="AM11" s="33"/>
+      <c r="AN11" s="33"/>
+      <c r="AO11" s="33"/>
+      <c r="AP11" s="33"/>
+      <c r="AQ11" s="67"/>
+      <c r="AR11" s="67"/>
+      <c r="AS11" s="33"/>
+      <c r="AT11" s="33"/>
+      <c r="AU11" s="33"/>
+      <c r="AV11" s="33"/>
+      <c r="AW11" s="34"/>
+      <c r="AY11" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="AZ11" s="77">
+      <c r="AZ11" s="76">
         <f>SUM(C17:AW17)</f>
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="99"/>
+      <c r="A12" s="109"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="19"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="21"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="21"/>
-      <c r="Y12" s="21"/>
-      <c r="Z12" s="23"/>
-      <c r="AA12" s="21"/>
-      <c r="AB12" s="21"/>
-      <c r="AC12" s="41"/>
-      <c r="AD12" s="59"/>
-      <c r="AE12" s="21"/>
-      <c r="AF12" s="21"/>
-      <c r="AG12" s="21"/>
-      <c r="AH12" s="21"/>
-      <c r="AI12" s="22"/>
-      <c r="AJ12" s="69"/>
-      <c r="AK12" s="69"/>
-      <c r="AL12" s="36"/>
-      <c r="AM12" s="36"/>
-      <c r="AN12" s="36"/>
-      <c r="AO12" s="36"/>
-      <c r="AP12" s="36"/>
-      <c r="AQ12" s="69"/>
-      <c r="AR12" s="69"/>
-      <c r="AS12" s="36"/>
-      <c r="AT12" s="36"/>
-      <c r="AU12" s="36"/>
-      <c r="AV12" s="36"/>
-      <c r="AW12" s="37"/>
-      <c r="AY12" s="77" t="s">
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="117"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="40"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="40"/>
+      <c r="AD12" s="58"/>
+      <c r="AE12" s="20"/>
+      <c r="AF12" s="20"/>
+      <c r="AG12" s="20"/>
+      <c r="AH12" s="20"/>
+      <c r="AI12" s="21"/>
+      <c r="AJ12" s="68"/>
+      <c r="AK12" s="68"/>
+      <c r="AL12" s="35"/>
+      <c r="AM12" s="35"/>
+      <c r="AN12" s="35"/>
+      <c r="AO12" s="35"/>
+      <c r="AP12" s="35"/>
+      <c r="AQ12" s="68"/>
+      <c r="AR12" s="68"/>
+      <c r="AS12" s="35"/>
+      <c r="AT12" s="35"/>
+      <c r="AU12" s="35"/>
+      <c r="AV12" s="35"/>
+      <c r="AW12" s="36"/>
+      <c r="AY12" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="AZ12" s="77">
+      <c r="AZ12" s="76">
         <f>SUM(C20:AW20)</f>
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="97" t="s">
+      <c r="A13" s="107" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -4712,168 +4733,167 @@
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
       <c r="G13" s="14"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
       <c r="J13" s="15"/>
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
       <c r="N13" s="13"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="40"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="39"/>
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
       <c r="S13" s="13"/>
       <c r="T13" s="13"/>
       <c r="U13" s="15"/>
-      <c r="V13" s="54"/>
-      <c r="W13" s="54"/>
+      <c r="V13" s="53"/>
+      <c r="W13" s="53"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
       <c r="Z13" s="15"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="13"/>
-      <c r="AC13" s="40"/>
-      <c r="AD13" s="55"/>
+      <c r="AC13" s="39"/>
+      <c r="AD13" s="54"/>
       <c r="AE13" s="13"/>
       <c r="AF13" s="13"/>
       <c r="AG13" s="13"/>
       <c r="AH13" s="13"/>
       <c r="AI13" s="14"/>
-      <c r="AJ13" s="67"/>
-      <c r="AK13" s="67"/>
-      <c r="AL13" s="38"/>
-      <c r="AM13" s="38"/>
-      <c r="AN13" s="38"/>
-      <c r="AO13" s="38"/>
-      <c r="AP13" s="38"/>
-      <c r="AQ13" s="67"/>
-      <c r="AR13" s="67"/>
-      <c r="AS13" s="38"/>
-      <c r="AT13" s="38"/>
-      <c r="AU13" s="38"/>
-      <c r="AV13" s="38"/>
-      <c r="AW13" s="39"/>
-      <c r="AY13" s="77" t="s">
+      <c r="AJ13" s="66"/>
+      <c r="AK13" s="66"/>
+      <c r="AL13" s="37"/>
+      <c r="AM13" s="37"/>
+      <c r="AN13" s="37"/>
+      <c r="AO13" s="37"/>
+      <c r="AP13" s="37"/>
+      <c r="AQ13" s="66"/>
+      <c r="AR13" s="66"/>
+      <c r="AS13" s="37"/>
+      <c r="AT13" s="37"/>
+      <c r="AU13" s="37"/>
+      <c r="AV13" s="37"/>
+      <c r="AW13" s="38"/>
+      <c r="AY13" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="AZ13" s="77">
+      <c r="AZ13" s="76">
         <f>SUM(C23:AW23)</f>
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A14" s="98"/>
+      <c r="A14" s="108"/>
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="26"/>
-      <c r="T14" s="26"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="61"/>
-      <c r="W14" s="61"/>
-      <c r="X14" s="82">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="82">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="26"/>
-      <c r="AC14" s="47"/>
-      <c r="AD14" s="58"/>
-      <c r="AE14" s="26"/>
-      <c r="AF14" s="26"/>
-      <c r="AG14" s="26"/>
-      <c r="AH14" s="26"/>
-      <c r="AI14" s="28"/>
-      <c r="AJ14" s="68"/>
-      <c r="AK14" s="68"/>
-      <c r="AL14" s="34"/>
-      <c r="AM14" s="34"/>
-      <c r="AN14" s="34"/>
-      <c r="AO14" s="34"/>
-      <c r="AP14" s="34"/>
-      <c r="AQ14" s="68"/>
-      <c r="AR14" s="68"/>
-      <c r="AS14" s="34"/>
-      <c r="AT14" s="34"/>
-      <c r="AU14" s="34"/>
-      <c r="AV14" s="34"/>
-      <c r="AW14" s="35"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="28"/>
+      <c r="V14" s="60"/>
+      <c r="W14" s="60"/>
+      <c r="X14" s="81">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="81">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="28"/>
+      <c r="AA14" s="28"/>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="46"/>
+      <c r="AD14" s="57"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="25"/>
+      <c r="AH14" s="25"/>
+      <c r="AI14" s="27"/>
+      <c r="AJ14" s="67"/>
+      <c r="AK14" s="67"/>
+      <c r="AL14" s="33"/>
+      <c r="AM14" s="33"/>
+      <c r="AN14" s="33"/>
+      <c r="AO14" s="33"/>
+      <c r="AP14" s="33"/>
+      <c r="AQ14" s="67"/>
+      <c r="AR14" s="67"/>
+      <c r="AS14" s="33"/>
+      <c r="AT14" s="33"/>
+      <c r="AU14" s="33"/>
+      <c r="AV14" s="33"/>
+      <c r="AW14" s="34"/>
     </row>
     <row r="15" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="99"/>
+      <c r="A15" s="109"/>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="19"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="59"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="62"/>
-      <c r="W15" s="62"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="23"/>
-      <c r="AA15" s="23"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="41"/>
-      <c r="AD15" s="59"/>
-      <c r="AE15" s="21"/>
-      <c r="AF15" s="21"/>
-      <c r="AG15" s="21"/>
-      <c r="AH15" s="21"/>
-      <c r="AI15" s="22"/>
-      <c r="AJ15" s="69"/>
-      <c r="AK15" s="69"/>
-      <c r="AL15" s="36"/>
-      <c r="AM15" s="36"/>
-      <c r="AN15" s="36"/>
-      <c r="AO15" s="36"/>
-      <c r="AP15" s="36"/>
-      <c r="AQ15" s="69"/>
-      <c r="AR15" s="69"/>
-      <c r="AS15" s="36"/>
-      <c r="AT15" s="36"/>
-      <c r="AU15" s="36"/>
-      <c r="AV15" s="36"/>
-      <c r="AW15" s="37"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="61"/>
+      <c r="W15" s="61"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="40"/>
+      <c r="AD15" s="58"/>
+      <c r="AE15" s="20"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="20"/>
+      <c r="AH15" s="20"/>
+      <c r="AI15" s="21"/>
+      <c r="AJ15" s="68"/>
+      <c r="AK15" s="68"/>
+      <c r="AL15" s="35"/>
+      <c r="AM15" s="35"/>
+      <c r="AN15" s="35"/>
+      <c r="AO15" s="35"/>
+      <c r="AP15" s="35"/>
+      <c r="AQ15" s="68"/>
+      <c r="AR15" s="68"/>
+      <c r="AS15" s="35"/>
+      <c r="AT15" s="35"/>
+      <c r="AU15" s="35"/>
+      <c r="AV15" s="35"/>
+      <c r="AW15" s="36"/>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A16" s="97" t="s">
+      <c r="A16" s="107" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4884,199 +4904,195 @@
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
       <c r="G16" s="14"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
       <c r="J16" s="15"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
       <c r="S16" s="13"/>
       <c r="T16" s="13"/>
       <c r="U16" s="13"/>
-      <c r="V16" s="40"/>
-      <c r="W16" s="40"/>
+      <c r="V16" s="39"/>
+      <c r="W16" s="39"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
       <c r="Z16" s="13"/>
       <c r="AA16" s="13"/>
       <c r="AB16" s="13"/>
-      <c r="AC16" s="40"/>
-      <c r="AD16" s="40"/>
+      <c r="AC16" s="39"/>
+      <c r="AD16" s="39"/>
       <c r="AE16" s="13"/>
       <c r="AF16" s="13"/>
       <c r="AG16" s="13"/>
       <c r="AH16" s="13"/>
       <c r="AI16" s="14"/>
-      <c r="AJ16" s="67"/>
-      <c r="AK16" s="67"/>
-      <c r="AL16" s="38"/>
-      <c r="AM16" s="38"/>
-      <c r="AN16" s="38"/>
-      <c r="AO16" s="38"/>
-      <c r="AP16" s="38"/>
-      <c r="AQ16" s="67"/>
-      <c r="AR16" s="67"/>
-      <c r="AS16" s="38"/>
-      <c r="AT16" s="38"/>
-      <c r="AU16" s="38"/>
-      <c r="AV16" s="38"/>
-      <c r="AW16" s="39"/>
+      <c r="AJ16" s="66"/>
+      <c r="AK16" s="66"/>
+      <c r="AL16" s="37"/>
+      <c r="AM16" s="37"/>
+      <c r="AN16" s="37"/>
+      <c r="AO16" s="37"/>
+      <c r="AP16" s="37"/>
+      <c r="AQ16" s="66"/>
+      <c r="AR16" s="66"/>
+      <c r="AS16" s="37"/>
+      <c r="AT16" s="37"/>
+      <c r="AU16" s="37"/>
+      <c r="AV16" s="37"/>
+      <c r="AW16" s="38"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A17" s="98"/>
+      <c r="A17" s="108"/>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="47"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="83">
-        <v>1</v>
-      </c>
-      <c r="R17" s="83">
-        <v>1</v>
-      </c>
-      <c r="S17" s="83">
-        <v>1</v>
-      </c>
-      <c r="T17" s="83">
-        <v>1</v>
-      </c>
-      <c r="U17" s="83">
-        <v>1</v>
-      </c>
-      <c r="V17" s="47"/>
-      <c r="W17" s="47"/>
-      <c r="X17" s="29"/>
-      <c r="Y17" s="26"/>
-      <c r="Z17" s="83">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="83">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="83">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="47"/>
-      <c r="AD17" s="47"/>
-      <c r="AE17" s="83">
-        <v>1</v>
-      </c>
-      <c r="AF17" s="83">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="83">
-        <v>1</v>
-      </c>
-      <c r="AH17" s="83">
-        <v>1</v>
-      </c>
-      <c r="AI17" s="84">
-        <v>1</v>
-      </c>
-      <c r="AJ17" s="68"/>
-      <c r="AK17" s="68"/>
-      <c r="AL17" s="85">
-        <v>1</v>
-      </c>
-      <c r="AM17" s="85">
-        <v>1</v>
-      </c>
-      <c r="AN17" s="85">
-        <v>1</v>
-      </c>
-      <c r="AO17" s="85">
-        <v>1</v>
-      </c>
-      <c r="AP17" s="85">
-        <v>1</v>
-      </c>
-      <c r="AQ17" s="68"/>
-      <c r="AR17" s="68"/>
-      <c r="AS17" s="85">
-        <v>1</v>
-      </c>
-      <c r="AT17" s="85">
-        <v>1</v>
-      </c>
-      <c r="AU17" s="85">
-        <v>1</v>
-      </c>
-      <c r="AV17" s="86"/>
-      <c r="AW17" s="35"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="82">
+        <v>1</v>
+      </c>
+      <c r="T17" s="82">
+        <v>1</v>
+      </c>
+      <c r="U17" s="82">
+        <v>1</v>
+      </c>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="28"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="82">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="82">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="82">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="46"/>
+      <c r="AD17" s="46"/>
+      <c r="AE17" s="82">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="82">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="82">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="82">
+        <v>1</v>
+      </c>
+      <c r="AI17" s="83">
+        <v>1</v>
+      </c>
+      <c r="AJ17" s="67"/>
+      <c r="AK17" s="67"/>
+      <c r="AL17" s="84">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="84">
+        <v>1</v>
+      </c>
+      <c r="AN17" s="84">
+        <v>1</v>
+      </c>
+      <c r="AO17" s="84">
+        <v>1</v>
+      </c>
+      <c r="AP17" s="84">
+        <v>1</v>
+      </c>
+      <c r="AQ17" s="67"/>
+      <c r="AR17" s="67"/>
+      <c r="AS17" s="84">
+        <v>1</v>
+      </c>
+      <c r="AT17" s="84">
+        <v>1</v>
+      </c>
+      <c r="AU17" s="84">
+        <v>1</v>
+      </c>
+      <c r="AV17" s="85"/>
+      <c r="AW17" s="34"/>
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="99"/>
+      <c r="A18" s="109"/>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="19"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="41"/>
-      <c r="W18" s="41"/>
-      <c r="X18" s="21"/>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="21"/>
-      <c r="AB18" s="21"/>
-      <c r="AC18" s="41"/>
-      <c r="AD18" s="41"/>
-      <c r="AE18" s="21"/>
-      <c r="AF18" s="21"/>
-      <c r="AG18" s="21"/>
-      <c r="AH18" s="21"/>
-      <c r="AI18" s="22"/>
-      <c r="AJ18" s="69"/>
-      <c r="AK18" s="69"/>
-      <c r="AL18" s="36"/>
-      <c r="AM18" s="36"/>
-      <c r="AN18" s="36"/>
-      <c r="AO18" s="36"/>
-      <c r="AP18" s="36"/>
-      <c r="AQ18" s="69"/>
-      <c r="AR18" s="69"/>
-      <c r="AS18" s="36"/>
-      <c r="AT18" s="36"/>
-      <c r="AU18" s="36"/>
-      <c r="AV18" s="36"/>
-      <c r="AW18" s="37"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="40"/>
+      <c r="W18" s="40"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="40"/>
+      <c r="AD18" s="40"/>
+      <c r="AE18" s="20"/>
+      <c r="AF18" s="20"/>
+      <c r="AG18" s="20"/>
+      <c r="AH18" s="20"/>
+      <c r="AI18" s="21"/>
+      <c r="AJ18" s="68"/>
+      <c r="AK18" s="68"/>
+      <c r="AL18" s="35"/>
+      <c r="AM18" s="35"/>
+      <c r="AN18" s="35"/>
+      <c r="AO18" s="35"/>
+      <c r="AP18" s="35"/>
+      <c r="AQ18" s="68"/>
+      <c r="AR18" s="68"/>
+      <c r="AS18" s="35"/>
+      <c r="AT18" s="35"/>
+      <c r="AU18" s="35"/>
+      <c r="AV18" s="35"/>
+      <c r="AW18" s="36"/>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A19" s="97" t="s">
+      <c r="A19" s="107" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -5087,173 +5103,173 @@
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
       <c r="G19" s="14"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
       <c r="J19" s="15"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
-      <c r="O19" s="55"/>
-      <c r="P19" s="40"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="39"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
       <c r="S19" s="13"/>
       <c r="T19" s="13"/>
       <c r="U19" s="13"/>
-      <c r="V19" s="40"/>
-      <c r="W19" s="40"/>
+      <c r="V19" s="39"/>
+      <c r="W19" s="39"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
       <c r="Z19" s="15"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="13"/>
-      <c r="AC19" s="40"/>
-      <c r="AD19" s="40"/>
+      <c r="AC19" s="39"/>
+      <c r="AD19" s="39"/>
       <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
       <c r="AI19" s="14"/>
-      <c r="AJ19" s="67"/>
-      <c r="AK19" s="67"/>
-      <c r="AL19" s="38"/>
-      <c r="AM19" s="38"/>
-      <c r="AN19" s="38"/>
-      <c r="AO19" s="38"/>
-      <c r="AP19" s="38"/>
-      <c r="AQ19" s="67"/>
-      <c r="AR19" s="67"/>
-      <c r="AS19" s="38"/>
-      <c r="AT19" s="38"/>
-      <c r="AU19" s="38"/>
-      <c r="AV19" s="38"/>
-      <c r="AW19" s="39"/>
+      <c r="AJ19" s="66"/>
+      <c r="AK19" s="66"/>
+      <c r="AL19" s="37"/>
+      <c r="AM19" s="37"/>
+      <c r="AN19" s="37"/>
+      <c r="AO19" s="37"/>
+      <c r="AP19" s="37"/>
+      <c r="AQ19" s="66"/>
+      <c r="AR19" s="66"/>
+      <c r="AS19" s="37"/>
+      <c r="AT19" s="37"/>
+      <c r="AU19" s="37"/>
+      <c r="AV19" s="37"/>
+      <c r="AW19" s="38"/>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A20" s="98"/>
+      <c r="A20" s="108"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="58"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="26"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="87">
-        <v>1</v>
-      </c>
-      <c r="V20" s="47"/>
-      <c r="W20" s="47"/>
-      <c r="X20" s="87">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="87">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="88">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="87">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="87">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="47"/>
-      <c r="AD20" s="58"/>
-      <c r="AE20" s="87">
-        <v>1</v>
-      </c>
-      <c r="AF20" s="87">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="26"/>
-      <c r="AH20" s="26"/>
-      <c r="AI20" s="28"/>
-      <c r="AJ20" s="68"/>
-      <c r="AK20" s="68"/>
-      <c r="AL20" s="34"/>
-      <c r="AM20" s="34"/>
-      <c r="AN20" s="34"/>
-      <c r="AO20" s="34"/>
-      <c r="AP20" s="34"/>
-      <c r="AQ20" s="68"/>
-      <c r="AR20" s="68"/>
-      <c r="AS20" s="34"/>
-      <c r="AT20" s="34"/>
-      <c r="AU20" s="34"/>
-      <c r="AV20" s="34"/>
-      <c r="AW20" s="35"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="57"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="86">
+        <v>1</v>
+      </c>
+      <c r="V20" s="46"/>
+      <c r="W20" s="46"/>
+      <c r="X20" s="86">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="86">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="87">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="86">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="86">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="46"/>
+      <c r="AD20" s="57"/>
+      <c r="AE20" s="86">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="86">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="25"/>
+      <c r="AH20" s="25"/>
+      <c r="AI20" s="27"/>
+      <c r="AJ20" s="67"/>
+      <c r="AK20" s="67"/>
+      <c r="AL20" s="33"/>
+      <c r="AM20" s="33"/>
+      <c r="AN20" s="33"/>
+      <c r="AO20" s="33"/>
+      <c r="AP20" s="33"/>
+      <c r="AQ20" s="67"/>
+      <c r="AR20" s="67"/>
+      <c r="AS20" s="33"/>
+      <c r="AT20" s="33"/>
+      <c r="AU20" s="33"/>
+      <c r="AV20" s="33"/>
+      <c r="AW20" s="34"/>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="99"/>
+      <c r="A21" s="109"/>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="19"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="41"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="41"/>
-      <c r="W21" s="41"/>
-      <c r="X21" s="21"/>
-      <c r="Y21" s="21"/>
-      <c r="Z21" s="23"/>
-      <c r="AA21" s="21"/>
-      <c r="AB21" s="21"/>
-      <c r="AC21" s="41"/>
-      <c r="AD21" s="59"/>
-      <c r="AE21" s="21"/>
-      <c r="AF21" s="21"/>
-      <c r="AG21" s="21"/>
-      <c r="AH21" s="21"/>
-      <c r="AI21" s="22"/>
-      <c r="AJ21" s="69"/>
-      <c r="AK21" s="69"/>
-      <c r="AL21" s="36"/>
-      <c r="AM21" s="36"/>
-      <c r="AN21" s="36"/>
-      <c r="AO21" s="36"/>
-      <c r="AP21" s="36"/>
-      <c r="AQ21" s="69"/>
-      <c r="AR21" s="69"/>
-      <c r="AS21" s="36"/>
-      <c r="AT21" s="36"/>
-      <c r="AU21" s="36"/>
-      <c r="AV21" s="36"/>
-      <c r="AW21" s="37"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="40"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="40"/>
+      <c r="AD21" s="58"/>
+      <c r="AE21" s="20"/>
+      <c r="AF21" s="20"/>
+      <c r="AG21" s="20"/>
+      <c r="AH21" s="20"/>
+      <c r="AI21" s="21"/>
+      <c r="AJ21" s="68"/>
+      <c r="AK21" s="68"/>
+      <c r="AL21" s="35"/>
+      <c r="AM21" s="35"/>
+      <c r="AN21" s="35"/>
+      <c r="AO21" s="35"/>
+      <c r="AP21" s="35"/>
+      <c r="AQ21" s="68"/>
+      <c r="AR21" s="68"/>
+      <c r="AS21" s="35"/>
+      <c r="AT21" s="35"/>
+      <c r="AU21" s="35"/>
+      <c r="AV21" s="35"/>
+      <c r="AW21" s="36"/>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A22" s="97" t="s">
+      <c r="A22" s="107" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -5264,213 +5280,213 @@
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
       <c r="S22" s="13"/>
       <c r="T22" s="13"/>
       <c r="U22" s="13"/>
-      <c r="V22" s="40"/>
-      <c r="W22" s="40"/>
+      <c r="V22" s="39"/>
+      <c r="W22" s="39"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="13"/>
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
       <c r="AB22" s="13"/>
-      <c r="AC22" s="40"/>
-      <c r="AD22" s="40"/>
+      <c r="AC22" s="39"/>
+      <c r="AD22" s="39"/>
       <c r="AE22" s="13"/>
       <c r="AF22" s="13"/>
       <c r="AG22" s="13"/>
       <c r="AH22" s="13"/>
       <c r="AI22" s="14"/>
-      <c r="AJ22" s="67"/>
-      <c r="AK22" s="67"/>
-      <c r="AL22" s="38"/>
-      <c r="AM22" s="71" t="s">
+      <c r="AJ22" s="66"/>
+      <c r="AK22" s="66"/>
+      <c r="AL22" s="37"/>
+      <c r="AM22" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="AN22" s="38"/>
-      <c r="AO22" s="38"/>
-      <c r="AP22" s="38"/>
-      <c r="AQ22" s="67"/>
-      <c r="AR22" s="67"/>
-      <c r="AS22" s="38"/>
-      <c r="AT22" s="38"/>
-      <c r="AU22" s="38"/>
-      <c r="AV22" s="38"/>
-      <c r="AW22" s="39"/>
+      <c r="AN22" s="37"/>
+      <c r="AO22" s="37"/>
+      <c r="AP22" s="37"/>
+      <c r="AQ22" s="66"/>
+      <c r="AR22" s="66"/>
+      <c r="AS22" s="37"/>
+      <c r="AT22" s="37"/>
+      <c r="AU22" s="37"/>
+      <c r="AV22" s="37"/>
+      <c r="AW22" s="38"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A23" s="98"/>
+      <c r="A23" s="108"/>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="89">
-        <v>1</v>
-      </c>
-      <c r="D23" s="90">
-        <v>1</v>
-      </c>
-      <c r="E23" s="90">
-        <v>1</v>
-      </c>
-      <c r="F23" s="90">
-        <v>1</v>
-      </c>
-      <c r="G23" s="90">
-        <v>1</v>
-      </c>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="89">
-        <v>1</v>
-      </c>
-      <c r="K23" s="90">
-        <v>1</v>
-      </c>
-      <c r="L23" s="90">
-        <v>1</v>
-      </c>
-      <c r="M23" s="90">
-        <v>1</v>
-      </c>
-      <c r="N23" s="90">
-        <v>1</v>
-      </c>
-      <c r="O23" s="47"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="89">
-        <v>1</v>
-      </c>
-      <c r="R23" s="90">
-        <v>1</v>
-      </c>
-      <c r="S23" s="90">
-        <v>1</v>
-      </c>
-      <c r="T23" s="90">
-        <v>1</v>
-      </c>
-      <c r="U23" s="90">
-        <v>1</v>
-      </c>
-      <c r="V23" s="47"/>
-      <c r="W23" s="47"/>
-      <c r="X23" s="89">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="90">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="90">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="90">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="90">
-        <v>1</v>
-      </c>
-      <c r="AC23" s="47"/>
-      <c r="AD23" s="47"/>
-      <c r="AE23" s="89">
-        <v>1</v>
-      </c>
-      <c r="AF23" s="90">
-        <v>1</v>
-      </c>
-      <c r="AG23" s="90">
-        <v>1</v>
-      </c>
-      <c r="AH23" s="90">
-        <v>1</v>
-      </c>
-      <c r="AI23" s="90">
-        <v>1</v>
-      </c>
-      <c r="AJ23" s="68"/>
-      <c r="AK23" s="68"/>
-      <c r="AL23" s="89">
-        <v>1</v>
-      </c>
-      <c r="AM23" s="90">
-        <v>1</v>
-      </c>
-      <c r="AN23" s="26"/>
-      <c r="AO23" s="26"/>
-      <c r="AP23" s="26"/>
-      <c r="AQ23" s="68"/>
-      <c r="AR23" s="68"/>
-      <c r="AS23" s="34"/>
-      <c r="AT23" s="34"/>
-      <c r="AU23" s="34"/>
-      <c r="AV23" s="34"/>
-      <c r="AW23" s="35"/>
+      <c r="C23" s="88">
+        <v>1</v>
+      </c>
+      <c r="D23" s="89">
+        <v>1</v>
+      </c>
+      <c r="E23" s="89">
+        <v>1</v>
+      </c>
+      <c r="F23" s="89">
+        <v>1</v>
+      </c>
+      <c r="G23" s="89">
+        <v>1</v>
+      </c>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="88">
+        <v>1</v>
+      </c>
+      <c r="K23" s="89">
+        <v>1</v>
+      </c>
+      <c r="L23" s="89">
+        <v>1</v>
+      </c>
+      <c r="M23" s="89">
+        <v>1</v>
+      </c>
+      <c r="N23" s="89">
+        <v>1</v>
+      </c>
+      <c r="O23" s="46"/>
+      <c r="P23" s="46"/>
+      <c r="Q23" s="88">
+        <v>1</v>
+      </c>
+      <c r="R23" s="89">
+        <v>1</v>
+      </c>
+      <c r="S23" s="89">
+        <v>1</v>
+      </c>
+      <c r="T23" s="89">
+        <v>1</v>
+      </c>
+      <c r="U23" s="89">
+        <v>1</v>
+      </c>
+      <c r="V23" s="46"/>
+      <c r="W23" s="46"/>
+      <c r="X23" s="88">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="89">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="89">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="89">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="89">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="46"/>
+      <c r="AD23" s="46"/>
+      <c r="AE23" s="88">
+        <v>1</v>
+      </c>
+      <c r="AF23" s="89">
+        <v>1</v>
+      </c>
+      <c r="AG23" s="89">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="89">
+        <v>1</v>
+      </c>
+      <c r="AI23" s="89">
+        <v>1</v>
+      </c>
+      <c r="AJ23" s="67"/>
+      <c r="AK23" s="67"/>
+      <c r="AL23" s="88">
+        <v>1</v>
+      </c>
+      <c r="AM23" s="89">
+        <v>1</v>
+      </c>
+      <c r="AN23" s="25"/>
+      <c r="AO23" s="25"/>
+      <c r="AP23" s="25"/>
+      <c r="AQ23" s="67"/>
+      <c r="AR23" s="67"/>
+      <c r="AS23" s="33"/>
+      <c r="AT23" s="33"/>
+      <c r="AU23" s="33"/>
+      <c r="AV23" s="33"/>
+      <c r="AW23" s="34"/>
     </row>
     <row r="24" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="99"/>
+      <c r="A24" s="109"/>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="19"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-      <c r="V24" s="41"/>
-      <c r="W24" s="41"/>
-      <c r="X24" s="21"/>
-      <c r="Y24" s="21"/>
-      <c r="Z24" s="21"/>
-      <c r="AA24" s="21"/>
-      <c r="AB24" s="21"/>
-      <c r="AC24" s="41"/>
-      <c r="AD24" s="41"/>
-      <c r="AE24" s="21"/>
-      <c r="AF24" s="21"/>
-      <c r="AG24" s="21"/>
-      <c r="AH24" s="21"/>
-      <c r="AI24" s="22"/>
-      <c r="AJ24" s="69"/>
-      <c r="AK24" s="69"/>
-      <c r="AL24" s="36"/>
-      <c r="AM24" s="36"/>
-      <c r="AN24" s="36"/>
-      <c r="AO24" s="36"/>
-      <c r="AP24" s="36"/>
-      <c r="AQ24" s="69"/>
-      <c r="AR24" s="69"/>
-      <c r="AS24" s="36"/>
-      <c r="AT24" s="36"/>
-      <c r="AU24" s="36"/>
-      <c r="AV24" s="36"/>
-      <c r="AW24" s="37"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="118"/>
+      <c r="M24" s="118"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="40"/>
+      <c r="W24" s="40"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="40"/>
+      <c r="AD24" s="40"/>
+      <c r="AE24" s="20"/>
+      <c r="AF24" s="20"/>
+      <c r="AG24" s="20"/>
+      <c r="AH24" s="20"/>
+      <c r="AI24" s="21"/>
+      <c r="AJ24" s="68"/>
+      <c r="AK24" s="68"/>
+      <c r="AL24" s="35"/>
+      <c r="AM24" s="35"/>
+      <c r="AN24" s="35"/>
+      <c r="AO24" s="35"/>
+      <c r="AP24" s="35"/>
+      <c r="AQ24" s="68"/>
+      <c r="AR24" s="68"/>
+      <c r="AS24" s="35"/>
+      <c r="AT24" s="35"/>
+      <c r="AU24" s="35"/>
+      <c r="AV24" s="35"/>
+      <c r="AW24" s="36"/>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A25" s="97" t="s">
+      <c r="A25" s="107" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -5481,159 +5497,159 @@
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="14"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
       <c r="J25" s="15"/>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
       <c r="N25" s="13"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="40"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="39"/>
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
       <c r="S25" s="13"/>
       <c r="T25" s="13"/>
       <c r="U25" s="13"/>
-      <c r="V25" s="40"/>
-      <c r="W25" s="40"/>
+      <c r="V25" s="39"/>
+      <c r="W25" s="39"/>
       <c r="X25" s="13"/>
       <c r="Y25" s="13"/>
       <c r="Z25" s="15"/>
       <c r="AA25" s="13"/>
       <c r="AB25" s="13"/>
-      <c r="AC25" s="40"/>
-      <c r="AD25" s="55"/>
+      <c r="AC25" s="39"/>
+      <c r="AD25" s="54"/>
       <c r="AE25" s="13"/>
       <c r="AF25" s="13"/>
       <c r="AG25" s="13"/>
       <c r="AH25" s="13"/>
       <c r="AI25" s="14"/>
-      <c r="AJ25" s="67"/>
-      <c r="AK25" s="67"/>
-      <c r="AL25" s="38"/>
-      <c r="AM25" s="38"/>
-      <c r="AN25" s="38"/>
-      <c r="AO25" s="38"/>
-      <c r="AP25" s="71" t="s">
+      <c r="AJ25" s="66"/>
+      <c r="AK25" s="66"/>
+      <c r="AL25" s="37"/>
+      <c r="AM25" s="37"/>
+      <c r="AN25" s="37"/>
+      <c r="AO25" s="37"/>
+      <c r="AP25" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="AQ25" s="67"/>
-      <c r="AR25" s="67"/>
-      <c r="AS25" s="38"/>
-      <c r="AT25" s="38"/>
-      <c r="AU25" s="38"/>
-      <c r="AV25" s="38"/>
-      <c r="AW25" s="39"/>
+      <c r="AQ25" s="66"/>
+      <c r="AR25" s="66"/>
+      <c r="AS25" s="37"/>
+      <c r="AT25" s="37"/>
+      <c r="AU25" s="37"/>
+      <c r="AV25" s="37"/>
+      <c r="AW25" s="38"/>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A26" s="98"/>
+      <c r="A26" s="108"/>
       <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="25"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="58"/>
-      <c r="P26" s="47"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-      <c r="V26" s="47"/>
-      <c r="W26" s="47"/>
-      <c r="X26" s="26"/>
-      <c r="Y26" s="26"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="26"/>
-      <c r="AB26" s="26"/>
-      <c r="AC26" s="47"/>
-      <c r="AD26" s="58"/>
-      <c r="AE26" s="26"/>
-      <c r="AF26" s="26"/>
-      <c r="AG26" s="28"/>
-      <c r="AH26" s="26"/>
-      <c r="AI26" s="28"/>
-      <c r="AJ26" s="68"/>
-      <c r="AK26" s="68"/>
-      <c r="AL26" s="34"/>
-      <c r="AM26" s="34"/>
-      <c r="AN26" s="34"/>
-      <c r="AO26" s="75"/>
-      <c r="AP26" s="75"/>
-      <c r="AQ26" s="68"/>
-      <c r="AR26" s="68"/>
-      <c r="AS26" s="34"/>
-      <c r="AT26" s="34"/>
-      <c r="AU26" s="75"/>
-      <c r="AV26" s="75"/>
-      <c r="AW26" s="76"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="25"/>
+      <c r="AC26" s="46"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="25"/>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="27"/>
+      <c r="AH26" s="25"/>
+      <c r="AI26" s="27"/>
+      <c r="AJ26" s="67"/>
+      <c r="AK26" s="67"/>
+      <c r="AL26" s="33"/>
+      <c r="AM26" s="33"/>
+      <c r="AN26" s="33"/>
+      <c r="AO26" s="74"/>
+      <c r="AP26" s="74"/>
+      <c r="AQ26" s="67"/>
+      <c r="AR26" s="67"/>
+      <c r="AS26" s="33"/>
+      <c r="AT26" s="33"/>
+      <c r="AU26" s="74"/>
+      <c r="AV26" s="74"/>
+      <c r="AW26" s="75"/>
     </row>
     <row r="27" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="99"/>
+      <c r="A27" s="109"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="19"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
-      <c r="O27" s="59"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
-      <c r="T27" s="21"/>
-      <c r="U27" s="21"/>
-      <c r="V27" s="41"/>
-      <c r="W27" s="41"/>
-      <c r="X27" s="21"/>
-      <c r="Y27" s="21"/>
-      <c r="Z27" s="23"/>
-      <c r="AA27" s="21"/>
-      <c r="AB27" s="21"/>
-      <c r="AC27" s="41"/>
-      <c r="AD27" s="59"/>
-      <c r="AE27" s="21"/>
-      <c r="AF27" s="21"/>
-      <c r="AG27" s="22"/>
-      <c r="AH27" s="21"/>
-      <c r="AI27" s="22"/>
-      <c r="AJ27" s="69"/>
-      <c r="AK27" s="69"/>
-      <c r="AL27" s="36"/>
-      <c r="AM27" s="36"/>
-      <c r="AN27" s="36"/>
-      <c r="AO27" s="36"/>
-      <c r="AP27" s="36"/>
-      <c r="AQ27" s="69"/>
-      <c r="AR27" s="69"/>
-      <c r="AS27" s="36"/>
-      <c r="AT27" s="36"/>
-      <c r="AU27" s="36"/>
-      <c r="AV27" s="36"/>
-      <c r="AW27" s="37"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="40"/>
+      <c r="W27" s="40"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="40"/>
+      <c r="AD27" s="58"/>
+      <c r="AE27" s="20"/>
+      <c r="AF27" s="20"/>
+      <c r="AG27" s="21"/>
+      <c r="AH27" s="20"/>
+      <c r="AI27" s="21"/>
+      <c r="AJ27" s="68"/>
+      <c r="AK27" s="68"/>
+      <c r="AL27" s="35"/>
+      <c r="AM27" s="35"/>
+      <c r="AN27" s="35"/>
+      <c r="AO27" s="35"/>
+      <c r="AP27" s="35"/>
+      <c r="AQ27" s="68"/>
+      <c r="AR27" s="68"/>
+      <c r="AS27" s="35"/>
+      <c r="AT27" s="35"/>
+      <c r="AU27" s="35"/>
+      <c r="AV27" s="35"/>
+      <c r="AW27" s="36"/>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A28" s="97" t="s">
+      <c r="A28" s="107" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -5644,319 +5660,319 @@
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
       <c r="G28" s="14"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
       <c r="J28" s="15"/>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
       <c r="N28" s="13"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="40"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="39"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
       <c r="S28" s="13"/>
       <c r="T28" s="13"/>
       <c r="U28" s="13"/>
-      <c r="V28" s="40"/>
-      <c r="W28" s="40"/>
+      <c r="V28" s="39"/>
+      <c r="W28" s="39"/>
       <c r="X28" s="13"/>
       <c r="Y28" s="13"/>
       <c r="Z28" s="15"/>
       <c r="AA28" s="13"/>
       <c r="AB28" s="13"/>
-      <c r="AC28" s="40"/>
-      <c r="AD28" s="55"/>
+      <c r="AC28" s="39"/>
+      <c r="AD28" s="54"/>
       <c r="AE28" s="13"/>
       <c r="AF28" s="13"/>
       <c r="AG28" s="13"/>
       <c r="AH28" s="13"/>
       <c r="AI28" s="14"/>
-      <c r="AJ28" s="67"/>
-      <c r="AK28" s="67"/>
-      <c r="AL28" s="38"/>
-      <c r="AM28" s="38"/>
-      <c r="AN28" s="38"/>
-      <c r="AO28" s="38"/>
-      <c r="AP28" s="38"/>
-      <c r="AQ28" s="67"/>
-      <c r="AR28" s="67"/>
-      <c r="AS28" s="38"/>
-      <c r="AT28" s="38"/>
-      <c r="AU28" s="71" t="s">
+      <c r="AJ28" s="66"/>
+      <c r="AK28" s="66"/>
+      <c r="AL28" s="37"/>
+      <c r="AM28" s="37"/>
+      <c r="AN28" s="37"/>
+      <c r="AO28" s="37"/>
+      <c r="AP28" s="37"/>
+      <c r="AQ28" s="66"/>
+      <c r="AR28" s="66"/>
+      <c r="AS28" s="37"/>
+      <c r="AT28" s="37"/>
+      <c r="AU28" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="AV28" s="38"/>
-      <c r="AW28" s="39"/>
+      <c r="AV28" s="37"/>
+      <c r="AW28" s="38"/>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A29" s="98"/>
+      <c r="A29" s="108"/>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="47"/>
-      <c r="W29" s="47"/>
-      <c r="X29" s="26"/>
-      <c r="Y29" s="26"/>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="26"/>
-      <c r="AC29" s="47"/>
-      <c r="AD29" s="58"/>
-      <c r="AE29" s="26"/>
-      <c r="AF29" s="26"/>
-      <c r="AG29" s="26"/>
-      <c r="AH29" s="26"/>
-      <c r="AI29" s="28"/>
-      <c r="AJ29" s="68"/>
-      <c r="AK29" s="68"/>
-      <c r="AL29" s="34"/>
-      <c r="AM29" s="34"/>
-      <c r="AN29" s="34"/>
-      <c r="AO29" s="34"/>
-      <c r="AP29" s="73"/>
-      <c r="AQ29" s="68"/>
-      <c r="AR29" s="68"/>
-      <c r="AS29" s="73"/>
-      <c r="AT29" s="73"/>
-      <c r="AU29" s="34"/>
-      <c r="AV29" s="34"/>
-      <c r="AW29" s="35"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="46"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="46"/>
+      <c r="W29" s="46"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="25"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="25"/>
+      <c r="AB29" s="25"/>
+      <c r="AC29" s="46"/>
+      <c r="AD29" s="57"/>
+      <c r="AE29" s="25"/>
+      <c r="AF29" s="25"/>
+      <c r="AG29" s="25"/>
+      <c r="AH29" s="25"/>
+      <c r="AI29" s="27"/>
+      <c r="AJ29" s="67"/>
+      <c r="AK29" s="67"/>
+      <c r="AL29" s="33"/>
+      <c r="AM29" s="33"/>
+      <c r="AN29" s="33"/>
+      <c r="AO29" s="33"/>
+      <c r="AP29" s="72"/>
+      <c r="AQ29" s="67"/>
+      <c r="AR29" s="67"/>
+      <c r="AS29" s="72"/>
+      <c r="AT29" s="72"/>
+      <c r="AU29" s="33"/>
+      <c r="AV29" s="33"/>
+      <c r="AW29" s="34"/>
     </row>
     <row r="30" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="99"/>
+      <c r="A30" s="109"/>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="19"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="59"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="21"/>
-      <c r="S30" s="21"/>
-      <c r="T30" s="21"/>
-      <c r="U30" s="21"/>
-      <c r="V30" s="41"/>
-      <c r="W30" s="41"/>
-      <c r="X30" s="21"/>
-      <c r="Y30" s="21"/>
-      <c r="Z30" s="23"/>
-      <c r="AA30" s="21"/>
-      <c r="AB30" s="21"/>
-      <c r="AC30" s="41"/>
-      <c r="AD30" s="59"/>
-      <c r="AE30" s="21"/>
-      <c r="AF30" s="21"/>
-      <c r="AG30" s="21"/>
-      <c r="AH30" s="21"/>
-      <c r="AI30" s="22"/>
-      <c r="AJ30" s="69"/>
-      <c r="AK30" s="69"/>
-      <c r="AL30" s="36"/>
-      <c r="AM30" s="36"/>
-      <c r="AN30" s="36"/>
-      <c r="AO30" s="36"/>
-      <c r="AP30" s="36"/>
-      <c r="AQ30" s="69"/>
-      <c r="AR30" s="69"/>
-      <c r="AS30" s="36"/>
-      <c r="AT30" s="36"/>
-      <c r="AU30" s="36"/>
-      <c r="AV30" s="36"/>
-      <c r="AW30" s="37"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="40"/>
+      <c r="W30" s="40"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="20"/>
+      <c r="AB30" s="20"/>
+      <c r="AC30" s="40"/>
+      <c r="AD30" s="58"/>
+      <c r="AE30" s="20"/>
+      <c r="AF30" s="20"/>
+      <c r="AG30" s="20"/>
+      <c r="AH30" s="20"/>
+      <c r="AI30" s="21"/>
+      <c r="AJ30" s="68"/>
+      <c r="AK30" s="68"/>
+      <c r="AL30" s="35"/>
+      <c r="AM30" s="35"/>
+      <c r="AN30" s="35"/>
+      <c r="AO30" s="35"/>
+      <c r="AP30" s="35"/>
+      <c r="AQ30" s="68"/>
+      <c r="AR30" s="68"/>
+      <c r="AS30" s="35"/>
+      <c r="AT30" s="35"/>
+      <c r="AU30" s="35"/>
+      <c r="AV30" s="35"/>
+      <c r="AW30" s="36"/>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A31" s="97" t="s">
+      <c r="A31" s="107" t="s">
         <v>21</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="70"/>
+      <c r="C31" s="69"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
       <c r="G31" s="17"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
       <c r="J31" s="18"/>
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
-      <c r="O31" s="60"/>
-      <c r="P31" s="42"/>
+      <c r="O31" s="59"/>
+      <c r="P31" s="41"/>
       <c r="Q31" s="16"/>
       <c r="R31" s="16"/>
       <c r="S31" s="16"/>
       <c r="T31" s="16"/>
       <c r="U31" s="16"/>
-      <c r="V31" s="42"/>
-      <c r="W31" s="42"/>
+      <c r="V31" s="41"/>
+      <c r="W31" s="41"/>
       <c r="X31" s="16"/>
       <c r="Y31" s="16"/>
       <c r="Z31" s="18"/>
       <c r="AA31" s="16"/>
       <c r="AB31" s="16"/>
-      <c r="AC31" s="42"/>
-      <c r="AD31" s="60"/>
+      <c r="AC31" s="41"/>
+      <c r="AD31" s="59"/>
       <c r="AE31" s="16"/>
       <c r="AF31" s="16"/>
       <c r="AG31" s="16"/>
       <c r="AH31" s="16"/>
       <c r="AI31" s="17"/>
-      <c r="AJ31" s="67"/>
-      <c r="AK31" s="67"/>
-      <c r="AL31" s="38"/>
+      <c r="AJ31" s="66"/>
+      <c r="AK31" s="66"/>
+      <c r="AL31" s="37"/>
       <c r="AM31" s="16"/>
-      <c r="AN31" s="38"/>
-      <c r="AO31" s="71" t="s">
+      <c r="AN31" s="37"/>
+      <c r="AO31" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="AP31" s="38"/>
-      <c r="AQ31" s="67"/>
-      <c r="AR31" s="67"/>
-      <c r="AS31" s="38"/>
-      <c r="AT31" s="38"/>
-      <c r="AU31" s="38"/>
-      <c r="AV31" s="38"/>
-      <c r="AW31" s="39"/>
+      <c r="AP31" s="37"/>
+      <c r="AQ31" s="66"/>
+      <c r="AR31" s="66"/>
+      <c r="AS31" s="37"/>
+      <c r="AT31" s="37"/>
+      <c r="AU31" s="37"/>
+      <c r="AV31" s="37"/>
+      <c r="AW31" s="38"/>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A32" s="98"/>
+      <c r="A32" s="108"/>
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="30"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="57"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="48"/>
-      <c r="W32" s="48"/>
-      <c r="X32" s="31"/>
-      <c r="Y32" s="31"/>
-      <c r="Z32" s="33"/>
-      <c r="AA32" s="31"/>
-      <c r="AB32" s="31"/>
-      <c r="AC32" s="48"/>
-      <c r="AD32" s="57"/>
-      <c r="AE32" s="31"/>
-      <c r="AF32" s="31"/>
-      <c r="AG32" s="31"/>
-      <c r="AH32" s="31"/>
-      <c r="AI32" s="32"/>
-      <c r="AJ32" s="68"/>
-      <c r="AK32" s="68"/>
-      <c r="AL32" s="34"/>
-      <c r="AM32" s="34"/>
-      <c r="AN32" s="74"/>
-      <c r="AO32" s="34"/>
-      <c r="AP32" s="34"/>
-      <c r="AQ32" s="68"/>
-      <c r="AR32" s="68"/>
-      <c r="AS32" s="34"/>
-      <c r="AT32" s="34"/>
-      <c r="AU32" s="34"/>
-      <c r="AV32" s="34"/>
-      <c r="AW32" s="35"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="47"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="47"/>
+      <c r="W32" s="47"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="32"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="47"/>
+      <c r="AD32" s="56"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
+      <c r="AG32" s="30"/>
+      <c r="AH32" s="30"/>
+      <c r="AI32" s="31"/>
+      <c r="AJ32" s="67"/>
+      <c r="AK32" s="67"/>
+      <c r="AL32" s="33"/>
+      <c r="AM32" s="33"/>
+      <c r="AN32" s="73"/>
+      <c r="AO32" s="33"/>
+      <c r="AP32" s="33"/>
+      <c r="AQ32" s="67"/>
+      <c r="AR32" s="67"/>
+      <c r="AS32" s="33"/>
+      <c r="AT32" s="33"/>
+      <c r="AU32" s="33"/>
+      <c r="AV32" s="33"/>
+      <c r="AW32" s="34"/>
     </row>
     <row r="33" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="100"/>
+      <c r="A33" s="110"/>
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="19"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="59"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="21"/>
-      <c r="R33" s="21"/>
-      <c r="S33" s="21"/>
-      <c r="T33" s="21"/>
-      <c r="U33" s="21"/>
-      <c r="V33" s="41"/>
-      <c r="W33" s="41"/>
-      <c r="X33" s="21"/>
-      <c r="Y33" s="21"/>
-      <c r="Z33" s="23"/>
-      <c r="AA33" s="21"/>
-      <c r="AB33" s="21"/>
-      <c r="AC33" s="41"/>
-      <c r="AD33" s="59"/>
-      <c r="AE33" s="21"/>
-      <c r="AF33" s="21"/>
-      <c r="AG33" s="21"/>
-      <c r="AH33" s="21"/>
-      <c r="AI33" s="22"/>
-      <c r="AJ33" s="69"/>
-      <c r="AK33" s="69"/>
-      <c r="AL33" s="36"/>
-      <c r="AM33" s="36"/>
-      <c r="AN33" s="36"/>
-      <c r="AO33" s="36"/>
-      <c r="AP33" s="36"/>
-      <c r="AQ33" s="69"/>
-      <c r="AR33" s="69"/>
-      <c r="AS33" s="36"/>
-      <c r="AT33" s="36"/>
-      <c r="AU33" s="36"/>
-      <c r="AV33" s="36"/>
-      <c r="AW33" s="37"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="58"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="40"/>
+      <c r="W33" s="40"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="20"/>
+      <c r="AB33" s="20"/>
+      <c r="AC33" s="40"/>
+      <c r="AD33" s="58"/>
+      <c r="AE33" s="20"/>
+      <c r="AF33" s="20"/>
+      <c r="AG33" s="20"/>
+      <c r="AH33" s="20"/>
+      <c r="AI33" s="21"/>
+      <c r="AJ33" s="68"/>
+      <c r="AK33" s="68"/>
+      <c r="AL33" s="35"/>
+      <c r="AM33" s="35"/>
+      <c r="AN33" s="35"/>
+      <c r="AO33" s="35"/>
+      <c r="AP33" s="35"/>
+      <c r="AQ33" s="68"/>
+      <c r="AR33" s="68"/>
+      <c r="AS33" s="35"/>
+      <c r="AT33" s="35"/>
+      <c r="AU33" s="35"/>
+      <c r="AV33" s="35"/>
+      <c r="AW33" s="36"/>
     </row>
     <row r="34" spans="1:49" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5991,13 +6007,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AL1:AP1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
@@ -6011,6 +6020,13 @@
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A19:A21"/>
+    <mergeCell ref="AL1:AP1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="X1:AB1"/>
+    <mergeCell ref="AE1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6038,14 +6054,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6284,27 +6298,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6329,9 +6336,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="505" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5F6DB47-6E14-4DE0-9B2D-D12C64557495}"/>
+  <xr:revisionPtr revIDLastSave="509" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{9735995C-247E-43C9-A6C1-90CCC759B4C9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
     <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1105,6 +1105,42 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1130,42 +1166,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3825,77 +3825,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="101">
-        <v>1</v>
-      </c>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="103"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="113">
+        <v>1</v>
+      </c>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="53"/>
       <c r="I1" s="54"/>
-      <c r="J1" s="101">
+      <c r="J1" s="113">
         <v>2</v>
       </c>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="103"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="115"/>
       <c r="O1" s="53"/>
       <c r="P1" s="54"/>
-      <c r="Q1" s="101">
+      <c r="Q1" s="113">
         <v>3</v>
       </c>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="103"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="115"/>
       <c r="V1" s="53"/>
       <c r="W1" s="54"/>
-      <c r="X1" s="101">
+      <c r="X1" s="113">
         <v>4</v>
       </c>
-      <c r="Y1" s="102"/>
-      <c r="Z1" s="102"/>
-      <c r="AA1" s="102"/>
-      <c r="AB1" s="103"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="115"/>
       <c r="AC1" s="53"/>
       <c r="AD1" s="54"/>
-      <c r="AE1" s="104">
+      <c r="AE1" s="116">
         <v>5</v>
       </c>
-      <c r="AF1" s="105"/>
-      <c r="AG1" s="105"/>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="106"/>
+      <c r="AF1" s="117"/>
+      <c r="AG1" s="117"/>
+      <c r="AH1" s="117"/>
+      <c r="AI1" s="118"/>
       <c r="AJ1" s="62"/>
       <c r="AK1" s="63"/>
-      <c r="AL1" s="98">
+      <c r="AL1" s="110">
         <v>6</v>
       </c>
-      <c r="AM1" s="99"/>
-      <c r="AN1" s="99"/>
-      <c r="AO1" s="99"/>
-      <c r="AP1" s="100"/>
+      <c r="AM1" s="111"/>
+      <c r="AN1" s="111"/>
+      <c r="AO1" s="111"/>
+      <c r="AP1" s="112"/>
       <c r="AQ1" s="62"/>
       <c r="AR1" s="63"/>
-      <c r="AS1" s="98">
+      <c r="AS1" s="110">
         <v>7</v>
       </c>
-      <c r="AT1" s="99"/>
-      <c r="AU1" s="99"/>
-      <c r="AV1" s="99"/>
-      <c r="AW1" s="100"/>
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="112"/>
     </row>
     <row r="2" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="114"/>
+      <c r="B2" s="107"/>
       <c r="C2" s="6">
         <v>1</v>
       </c>
@@ -4015,10 +4015,10 @@
       </c>
     </row>
     <row r="3" spans="1:52" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="115" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="108" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="109"/>
       <c r="C3" s="48">
         <v>45887</v>
       </c>
@@ -4162,7 +4162,7 @@
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="101" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4217,7 +4217,7 @@
       <c r="AW4" s="38"/>
     </row>
     <row r="5" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="108"/>
+      <c r="A5" s="101"/>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4276,7 +4276,7 @@
       <c r="AW5" s="34"/>
     </row>
     <row r="6" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="109"/>
+      <c r="A6" s="102"/>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
@@ -4335,7 +4335,7 @@
       </c>
     </row>
     <row r="7" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="107" t="s">
+      <c r="A7" s="100" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4399,7 +4399,7 @@
       </c>
     </row>
     <row r="8" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="108"/>
+      <c r="A8" s="101"/>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
@@ -4467,7 +4467,7 @@
       </c>
     </row>
     <row r="9" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="109"/>
+      <c r="A9" s="102"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -4527,7 +4527,7 @@
       </c>
     </row>
     <row r="10" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="107" t="s">
+      <c r="A10" s="100" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4590,7 +4590,7 @@
       </c>
     </row>
     <row r="11" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="108"/>
+      <c r="A11" s="101"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -4662,7 +4662,7 @@
       </c>
     </row>
     <row r="12" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="109"/>
+      <c r="A12" s="102"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -4676,12 +4676,12 @@
       <c r="J12" s="20"/>
       <c r="K12" s="20"/>
       <c r="L12" s="20"/>
-      <c r="M12" s="117"/>
-      <c r="N12" s="20"/>
+      <c r="M12" s="98"/>
+      <c r="N12" s="98"/>
       <c r="O12" s="40"/>
       <c r="P12" s="40"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
+      <c r="Q12" s="98"/>
+      <c r="R12" s="98"/>
       <c r="S12" s="20"/>
       <c r="T12" s="20"/>
       <c r="U12" s="20"/>
@@ -4722,7 +4722,7 @@
       </c>
     </row>
     <row r="13" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="107" t="s">
+      <c r="A13" s="100" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -4784,7 +4784,7 @@
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A14" s="108"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
@@ -4840,7 +4840,7 @@
       <c r="AW14" s="34"/>
     </row>
     <row r="15" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="109"/>
+      <c r="A15" s="102"/>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
@@ -4893,7 +4893,7 @@
       <c r="AW15" s="36"/>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A16" s="107" t="s">
+      <c r="A16" s="100" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4948,7 +4948,7 @@
       <c r="AW16" s="38"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A17" s="108"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
@@ -5039,7 +5039,7 @@
       <c r="AW17" s="34"/>
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109"/>
+      <c r="A18" s="102"/>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
@@ -5092,7 +5092,7 @@
       <c r="AW18" s="36"/>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A19" s="107" t="s">
+      <c r="A19" s="100" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -5147,7 +5147,7 @@
       <c r="AW19" s="38"/>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A20" s="108"/>
+      <c r="A20" s="101"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
@@ -5216,7 +5216,7 @@
       <c r="AW20" s="34"/>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="109"/>
+      <c r="A21" s="102"/>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
@@ -5269,7 +5269,7 @@
       <c r="AW21" s="36"/>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A22" s="107" t="s">
+      <c r="A22" s="100" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -5326,7 +5326,7 @@
       <c r="AW22" s="38"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A23" s="108"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
@@ -5433,24 +5433,24 @@
       <c r="AW23" s="34"/>
     </row>
     <row r="24" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="109"/>
+      <c r="A24" s="102"/>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="20"/>
       <c r="E24" s="20"/>
-      <c r="F24" s="118"/>
+      <c r="F24" s="99"/>
       <c r="G24" s="20"/>
       <c r="H24" s="40"/>
-      <c r="I24" s="118"/>
+      <c r="I24" s="99"/>
       <c r="J24" s="22"/>
       <c r="K24" s="20"/>
-      <c r="L24" s="118"/>
-      <c r="M24" s="118"/>
+      <c r="L24" s="99"/>
+      <c r="M24" s="99"/>
       <c r="N24" s="20"/>
       <c r="O24" s="40"/>
-      <c r="P24" s="40"/>
+      <c r="P24" s="99"/>
       <c r="Q24" s="20"/>
       <c r="R24" s="20"/>
       <c r="S24" s="20"/>
@@ -5486,7 +5486,7 @@
       <c r="AW24" s="36"/>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A25" s="107" t="s">
+      <c r="A25" s="100" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -5543,7 +5543,7 @@
       <c r="AW25" s="38"/>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A26" s="108"/>
+      <c r="A26" s="101"/>
       <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
@@ -5596,7 +5596,7 @@
       <c r="AW26" s="75"/>
     </row>
     <row r="27" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="109"/>
+      <c r="A27" s="102"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -5649,7 +5649,7 @@
       <c r="AW27" s="36"/>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A28" s="107" t="s">
+      <c r="A28" s="100" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -5706,7 +5706,7 @@
       <c r="AW28" s="38"/>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A29" s="108"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
@@ -5759,7 +5759,7 @@
       <c r="AW29" s="34"/>
     </row>
     <row r="30" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="109"/>
+      <c r="A30" s="102"/>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
@@ -5812,7 +5812,7 @@
       <c r="AW30" s="36"/>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A31" s="107" t="s">
+      <c r="A31" s="100" t="s">
         <v>21</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -5869,7 +5869,7 @@
       <c r="AW31" s="38"/>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A32" s="108"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -5922,7 +5922,7 @@
       <c r="AW32" s="34"/>
     </row>
     <row r="33" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="110"/>
+      <c r="A33" s="103"/>
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
@@ -6007,6 +6007,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AL1:AP1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="X1:AB1"/>
+    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
@@ -6020,13 +6027,6 @@
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="AL1:AP1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="AE1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6054,15 +6054,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="508407daaf082c5381f5a7b4d9841321">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d41ad40f3ea4d0f4b8e18c6becc727c2" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -6297,6 +6288,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6309,14 +6309,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D3E6B6-1954-499D-AE9A-4487E5EEA9C5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6331,6 +6323,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="509" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{9735995C-247E-43C9-A6C1-90CCC759B4C9}"/>
+  <xr:revisionPtr revIDLastSave="513" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{82EAE4C3-619F-4A25-9161-C5F919BBEA8B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
     <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -190,7 +190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,6 +305,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="43">
     <border>
@@ -852,7 +858,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1111,6 +1117,33 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1141,31 +1174,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3825,77 +3834,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="113">
-        <v>1</v>
-      </c>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="115"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="103">
+        <v>1</v>
+      </c>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="105"/>
       <c r="H1" s="53"/>
       <c r="I1" s="54"/>
-      <c r="J1" s="113">
+      <c r="J1" s="103">
         <v>2</v>
       </c>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="115"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="105"/>
       <c r="O1" s="53"/>
       <c r="P1" s="54"/>
-      <c r="Q1" s="113">
+      <c r="Q1" s="103">
         <v>3</v>
       </c>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="115"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="104"/>
+      <c r="T1" s="104"/>
+      <c r="U1" s="105"/>
       <c r="V1" s="53"/>
       <c r="W1" s="54"/>
-      <c r="X1" s="113">
+      <c r="X1" s="103">
         <v>4</v>
       </c>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="115"/>
+      <c r="Y1" s="104"/>
+      <c r="Z1" s="104"/>
+      <c r="AA1" s="104"/>
+      <c r="AB1" s="105"/>
       <c r="AC1" s="53"/>
       <c r="AD1" s="54"/>
-      <c r="AE1" s="116">
+      <c r="AE1" s="106">
         <v>5</v>
       </c>
-      <c r="AF1" s="117"/>
-      <c r="AG1" s="117"/>
-      <c r="AH1" s="117"/>
-      <c r="AI1" s="118"/>
+      <c r="AF1" s="107"/>
+      <c r="AG1" s="107"/>
+      <c r="AH1" s="107"/>
+      <c r="AI1" s="108"/>
       <c r="AJ1" s="62"/>
       <c r="AK1" s="63"/>
-      <c r="AL1" s="110">
+      <c r="AL1" s="100">
         <v>6</v>
       </c>
-      <c r="AM1" s="111"/>
-      <c r="AN1" s="111"/>
-      <c r="AO1" s="111"/>
-      <c r="AP1" s="112"/>
+      <c r="AM1" s="101"/>
+      <c r="AN1" s="101"/>
+      <c r="AO1" s="101"/>
+      <c r="AP1" s="102"/>
       <c r="AQ1" s="62"/>
       <c r="AR1" s="63"/>
-      <c r="AS1" s="110">
+      <c r="AS1" s="100">
         <v>7</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="112"/>
+      <c r="AT1" s="101"/>
+      <c r="AU1" s="101"/>
+      <c r="AV1" s="101"/>
+      <c r="AW1" s="102"/>
     </row>
     <row r="2" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="A2" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="107"/>
+      <c r="B2" s="116"/>
       <c r="C2" s="6">
         <v>1</v>
       </c>
@@ -4015,10 +4024,10 @@
       </c>
     </row>
     <row r="3" spans="1:52" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="108" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="109"/>
+      <c r="A3" s="117" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="48">
         <v>45887</v>
       </c>
@@ -4162,7 +4171,7 @@
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A4" s="101" t="s">
+      <c r="A4" s="110" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4217,7 +4226,7 @@
       <c r="AW4" s="38"/>
     </row>
     <row r="5" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="101"/>
+      <c r="A5" s="110"/>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4276,7 +4285,7 @@
       <c r="AW5" s="34"/>
     </row>
     <row r="6" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="102"/>
+      <c r="A6" s="111"/>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
@@ -4335,7 +4344,7 @@
       </c>
     </row>
     <row r="7" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="100" t="s">
+      <c r="A7" s="109" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4399,7 +4408,7 @@
       </c>
     </row>
     <row r="8" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="101"/>
+      <c r="A8" s="110"/>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
@@ -4467,7 +4476,7 @@
       </c>
     </row>
     <row r="9" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="102"/>
+      <c r="A9" s="111"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -4527,7 +4536,7 @@
       </c>
     </row>
     <row r="10" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="109" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4590,7 +4599,7 @@
       </c>
     </row>
     <row r="11" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="101"/>
+      <c r="A11" s="110"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -4662,7 +4671,7 @@
       </c>
     </row>
     <row r="12" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="102"/>
+      <c r="A12" s="111"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -4682,7 +4691,7 @@
       <c r="P12" s="40"/>
       <c r="Q12" s="98"/>
       <c r="R12" s="98"/>
-      <c r="S12" s="20"/>
+      <c r="S12" s="98"/>
       <c r="T12" s="20"/>
       <c r="U12" s="20"/>
       <c r="V12" s="40"/>
@@ -4722,7 +4731,7 @@
       </c>
     </row>
     <row r="13" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="100" t="s">
+      <c r="A13" s="109" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -4784,7 +4793,7 @@
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A14" s="101"/>
+      <c r="A14" s="110"/>
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
@@ -4840,7 +4849,7 @@
       <c r="AW14" s="34"/>
     </row>
     <row r="15" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="102"/>
+      <c r="A15" s="111"/>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
@@ -4893,7 +4902,7 @@
       <c r="AW15" s="36"/>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="109" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4948,7 +4957,7 @@
       <c r="AW16" s="38"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A17" s="101"/>
+      <c r="A17" s="110"/>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
@@ -5039,7 +5048,7 @@
       <c r="AW17" s="34"/>
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="102"/>
+      <c r="A18" s="111"/>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
@@ -5058,8 +5067,8 @@
       <c r="O18" s="40"/>
       <c r="P18" s="40"/>
       <c r="Q18" s="20"/>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="119"/>
       <c r="T18" s="20"/>
       <c r="U18" s="20"/>
       <c r="V18" s="40"/>
@@ -5092,7 +5101,7 @@
       <c r="AW18" s="36"/>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A19" s="100" t="s">
+      <c r="A19" s="109" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -5147,7 +5156,7 @@
       <c r="AW19" s="38"/>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A20" s="101"/>
+      <c r="A20" s="110"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
@@ -5216,7 +5225,7 @@
       <c r="AW20" s="34"/>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="102"/>
+      <c r="A21" s="111"/>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
@@ -5269,7 +5278,7 @@
       <c r="AW21" s="36"/>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A22" s="100" t="s">
+      <c r="A22" s="109" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -5326,7 +5335,7 @@
       <c r="AW22" s="38"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A23" s="101"/>
+      <c r="A23" s="110"/>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
@@ -5433,7 +5442,7 @@
       <c r="AW23" s="34"/>
     </row>
     <row r="24" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="102"/>
+      <c r="A24" s="111"/>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
@@ -5486,7 +5495,7 @@
       <c r="AW24" s="36"/>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A25" s="100" t="s">
+      <c r="A25" s="109" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -5543,7 +5552,7 @@
       <c r="AW25" s="38"/>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A26" s="101"/>
+      <c r="A26" s="110"/>
       <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
@@ -5596,7 +5605,7 @@
       <c r="AW26" s="75"/>
     </row>
     <row r="27" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="102"/>
+      <c r="A27" s="111"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -5649,7 +5658,7 @@
       <c r="AW27" s="36"/>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="109" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -5706,7 +5715,7 @@
       <c r="AW28" s="38"/>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A29" s="101"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
@@ -5759,7 +5768,7 @@
       <c r="AW29" s="34"/>
     </row>
     <row r="30" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="102"/>
+      <c r="A30" s="111"/>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
@@ -5812,7 +5821,7 @@
       <c r="AW30" s="36"/>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A31" s="100" t="s">
+      <c r="A31" s="109" t="s">
         <v>21</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -5869,7 +5878,7 @@
       <c r="AW31" s="38"/>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A32" s="101"/>
+      <c r="A32" s="110"/>
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -5922,7 +5931,7 @@
       <c r="AW32" s="34"/>
     </row>
     <row r="33" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="103"/>
+      <c r="A33" s="112"/>
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
@@ -6007,13 +6016,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AL1:AP1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
@@ -6027,6 +6029,13 @@
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A19:A21"/>
+    <mergeCell ref="AL1:AP1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="X1:AB1"/>
+    <mergeCell ref="AE1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6054,6 +6063,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="508407daaf082c5381f5a7b4d9841321">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d41ad40f3ea4d0f4b8e18c6becc727c2" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -6288,27 +6317,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D3E6B6-1954-499D-AE9A-4487E5EEA9C5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6325,29 +6359,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
@@ -10,14 +10,14 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="513" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{82EAE4C3-619F-4A25-9161-C5F919BBEA8B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4965" yWindow="3840" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
     <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1117,6 +1117,39 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1142,39 +1175,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3834,77 +3834,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="103">
-        <v>1</v>
-      </c>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="105"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="114">
+        <v>1</v>
+      </c>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="116"/>
       <c r="H1" s="53"/>
       <c r="I1" s="54"/>
-      <c r="J1" s="103">
+      <c r="J1" s="114">
         <v>2</v>
       </c>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="105"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="116"/>
       <c r="O1" s="53"/>
       <c r="P1" s="54"/>
-      <c r="Q1" s="103">
+      <c r="Q1" s="114">
         <v>3</v>
       </c>
-      <c r="R1" s="104"/>
-      <c r="S1" s="104"/>
-      <c r="T1" s="104"/>
-      <c r="U1" s="105"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="116"/>
       <c r="V1" s="53"/>
       <c r="W1" s="54"/>
-      <c r="X1" s="103">
+      <c r="X1" s="114">
         <v>4</v>
       </c>
-      <c r="Y1" s="104"/>
-      <c r="Z1" s="104"/>
-      <c r="AA1" s="104"/>
-      <c r="AB1" s="105"/>
+      <c r="Y1" s="115"/>
+      <c r="Z1" s="115"/>
+      <c r="AA1" s="115"/>
+      <c r="AB1" s="116"/>
       <c r="AC1" s="53"/>
       <c r="AD1" s="54"/>
-      <c r="AE1" s="106">
+      <c r="AE1" s="117">
         <v>5</v>
       </c>
-      <c r="AF1" s="107"/>
-      <c r="AG1" s="107"/>
-      <c r="AH1" s="107"/>
-      <c r="AI1" s="108"/>
+      <c r="AF1" s="118"/>
+      <c r="AG1" s="118"/>
+      <c r="AH1" s="118"/>
+      <c r="AI1" s="119"/>
       <c r="AJ1" s="62"/>
       <c r="AK1" s="63"/>
-      <c r="AL1" s="100">
+      <c r="AL1" s="111">
         <v>6</v>
       </c>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="101"/>
-      <c r="AO1" s="101"/>
-      <c r="AP1" s="102"/>
+      <c r="AM1" s="112"/>
+      <c r="AN1" s="112"/>
+      <c r="AO1" s="112"/>
+      <c r="AP1" s="113"/>
       <c r="AQ1" s="62"/>
       <c r="AR1" s="63"/>
-      <c r="AS1" s="100">
+      <c r="AS1" s="111">
         <v>7</v>
       </c>
-      <c r="AT1" s="101"/>
-      <c r="AU1" s="101"/>
-      <c r="AV1" s="101"/>
-      <c r="AW1" s="102"/>
+      <c r="AT1" s="112"/>
+      <c r="AU1" s="112"/>
+      <c r="AV1" s="112"/>
+      <c r="AW1" s="113"/>
     </row>
     <row r="2" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="116"/>
+      <c r="B2" s="108"/>
       <c r="C2" s="6">
         <v>1</v>
       </c>
@@ -4024,10 +4024,10 @@
       </c>
     </row>
     <row r="3" spans="1:52" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="117" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="110"/>
       <c r="C3" s="48">
         <v>45887</v>
       </c>
@@ -4171,7 +4171,7 @@
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A4" s="110" t="s">
+      <c r="A4" s="102" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4226,7 +4226,7 @@
       <c r="AW4" s="38"/>
     </row>
     <row r="5" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="110"/>
+      <c r="A5" s="102"/>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4285,7 +4285,7 @@
       <c r="AW5" s="34"/>
     </row>
     <row r="6" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="111"/>
+      <c r="A6" s="103"/>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
@@ -4344,7 +4344,7 @@
       </c>
     </row>
     <row r="7" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="101" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4408,7 +4408,7 @@
       </c>
     </row>
     <row r="8" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="110"/>
+      <c r="A8" s="102"/>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
@@ -4476,7 +4476,7 @@
       </c>
     </row>
     <row r="9" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="111"/>
+      <c r="A9" s="103"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -4536,7 +4536,7 @@
       </c>
     </row>
     <row r="10" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="109" t="s">
+      <c r="A10" s="101" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4599,7 +4599,7 @@
       </c>
     </row>
     <row r="11" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="110"/>
+      <c r="A11" s="102"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -4671,7 +4671,7 @@
       </c>
     </row>
     <row r="12" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="111"/>
+      <c r="A12" s="103"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -4731,7 +4731,7 @@
       </c>
     </row>
     <row r="13" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="109" t="s">
+      <c r="A13" s="101" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -4793,7 +4793,7 @@
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A14" s="110"/>
+      <c r="A14" s="102"/>
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
@@ -4849,7 +4849,7 @@
       <c r="AW14" s="34"/>
     </row>
     <row r="15" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="111"/>
+      <c r="A15" s="103"/>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
@@ -4902,7 +4902,7 @@
       <c r="AW15" s="36"/>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A16" s="109" t="s">
+      <c r="A16" s="101" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4957,7 +4957,7 @@
       <c r="AW16" s="38"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A17" s="110"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
@@ -5048,7 +5048,7 @@
       <c r="AW17" s="34"/>
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="111"/>
+      <c r="A18" s="103"/>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
@@ -5067,8 +5067,8 @@
       <c r="O18" s="40"/>
       <c r="P18" s="40"/>
       <c r="Q18" s="20"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
       <c r="T18" s="20"/>
       <c r="U18" s="20"/>
       <c r="V18" s="40"/>
@@ -5101,7 +5101,7 @@
       <c r="AW18" s="36"/>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A19" s="109" t="s">
+      <c r="A19" s="101" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -5156,7 +5156,7 @@
       <c r="AW19" s="38"/>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A20" s="110"/>
+      <c r="A20" s="102"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
@@ -5225,7 +5225,7 @@
       <c r="AW20" s="34"/>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="111"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
@@ -5278,7 +5278,7 @@
       <c r="AW21" s="36"/>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A22" s="109" t="s">
+      <c r="A22" s="101" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -5335,7 +5335,7 @@
       <c r="AW22" s="38"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A23" s="110"/>
+      <c r="A23" s="102"/>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
@@ -5442,7 +5442,7 @@
       <c r="AW23" s="34"/>
     </row>
     <row r="24" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="111"/>
+      <c r="A24" s="103"/>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
@@ -5495,7 +5495,7 @@
       <c r="AW24" s="36"/>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A25" s="109" t="s">
+      <c r="A25" s="101" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -5552,7 +5552,7 @@
       <c r="AW25" s="38"/>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A26" s="110"/>
+      <c r="A26" s="102"/>
       <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
@@ -5605,7 +5605,7 @@
       <c r="AW26" s="75"/>
     </row>
     <row r="27" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="111"/>
+      <c r="A27" s="103"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -5658,7 +5658,7 @@
       <c r="AW27" s="36"/>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A28" s="109" t="s">
+      <c r="A28" s="101" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -5715,7 +5715,7 @@
       <c r="AW28" s="38"/>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A29" s="110"/>
+      <c r="A29" s="102"/>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
@@ -5768,7 +5768,7 @@
       <c r="AW29" s="34"/>
     </row>
     <row r="30" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="111"/>
+      <c r="A30" s="103"/>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
@@ -5821,7 +5821,7 @@
       <c r="AW30" s="36"/>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A31" s="109" t="s">
+      <c r="A31" s="101" t="s">
         <v>21</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -5878,7 +5878,7 @@
       <c r="AW31" s="38"/>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A32" s="110"/>
+      <c r="A32" s="102"/>
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -5931,7 +5931,7 @@
       <c r="AW32" s="34"/>
     </row>
     <row r="33" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="112"/>
+      <c r="A33" s="104"/>
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
@@ -6016,6 +6016,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AL1:AP1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="X1:AB1"/>
+    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
@@ -6029,13 +6036,6 @@
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="AL1:AP1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="AE1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6063,26 +6063,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="508407daaf082c5381f5a7b4d9841321">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d41ad40f3ea4d0f4b8e18c6becc727c2" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -6317,32 +6297,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D3E6B6-1954-499D-AE9A-4487E5EEA9C5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6359,4 +6334,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="513" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{82EAE4C3-619F-4A25-9161-C5F919BBEA8B}"/>
+  <xr:revisionPtr revIDLastSave="534" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCAF0FC9-D685-4945-BDBE-CF431906686D}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4965" yWindow="3840" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
     <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -97,13 +97,13 @@
     <t>Jour</t>
   </si>
   <si>
-    <t>Documentation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Totaux </t>
   </si>
   <si>
     <t>théorique</t>
+  </si>
+  <si>
+    <t>Documentation (Affiche + Résumé)</t>
   </si>
 </sst>
 </file>
@@ -190,7 +190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,6 +311,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="43">
     <border>
@@ -858,7 +864,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1120,6 +1126,9 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1175,6 +1184,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1673,6 +1685,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1680,7 +1693,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -1802,7 +1814,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.18247179892699958"/>
+          <c:y val="0.24655960402875673"/>
+          <c:w val="0.49961081437850713"/>
+          <c:h val="0.75344039597124324"/>
+        </c:manualLayout>
+      </c:layout>
       <c:pieChart>
         <c:varyColors val="1"/>
         <c:ser>
@@ -2081,6 +2103,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2088,7 +2111,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -3425,16 +3447,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>478289</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>95860</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>78239</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>162535</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>33619</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>22412</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>147919</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>136712</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3461,16 +3483,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>5094</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>87710</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>52719</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>68660</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>271997</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>101768</xdr:rowOff>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3499,9 +3521,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3539,9 +3561,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3574,26 +3596,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3626,26 +3631,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3834,77 +3822,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="114">
-        <v>1</v>
-      </c>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="116"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="115">
+        <v>1</v>
+      </c>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="117"/>
       <c r="H1" s="53"/>
       <c r="I1" s="54"/>
-      <c r="J1" s="114">
+      <c r="J1" s="115">
         <v>2</v>
       </c>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="117"/>
       <c r="O1" s="53"/>
       <c r="P1" s="54"/>
-      <c r="Q1" s="114">
+      <c r="Q1" s="115">
         <v>3</v>
       </c>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="117"/>
       <c r="V1" s="53"/>
       <c r="W1" s="54"/>
-      <c r="X1" s="114">
+      <c r="X1" s="115">
         <v>4</v>
       </c>
-      <c r="Y1" s="115"/>
-      <c r="Z1" s="115"/>
-      <c r="AA1" s="115"/>
-      <c r="AB1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="53"/>
       <c r="AD1" s="54"/>
-      <c r="AE1" s="117">
+      <c r="AE1" s="118">
         <v>5</v>
       </c>
-      <c r="AF1" s="118"/>
-      <c r="AG1" s="118"/>
-      <c r="AH1" s="118"/>
-      <c r="AI1" s="119"/>
+      <c r="AF1" s="119"/>
+      <c r="AG1" s="119"/>
+      <c r="AH1" s="119"/>
+      <c r="AI1" s="120"/>
       <c r="AJ1" s="62"/>
       <c r="AK1" s="63"/>
-      <c r="AL1" s="111">
+      <c r="AL1" s="112">
         <v>6</v>
       </c>
-      <c r="AM1" s="112"/>
-      <c r="AN1" s="112"/>
-      <c r="AO1" s="112"/>
-      <c r="AP1" s="113"/>
+      <c r="AM1" s="113"/>
+      <c r="AN1" s="113"/>
+      <c r="AO1" s="113"/>
+      <c r="AP1" s="114"/>
       <c r="AQ1" s="62"/>
       <c r="AR1" s="63"/>
-      <c r="AS1" s="111">
+      <c r="AS1" s="112">
         <v>7</v>
       </c>
-      <c r="AT1" s="112"/>
-      <c r="AU1" s="112"/>
-      <c r="AV1" s="112"/>
-      <c r="AW1" s="113"/>
+      <c r="AT1" s="113"/>
+      <c r="AU1" s="113"/>
+      <c r="AV1" s="113"/>
+      <c r="AW1" s="114"/>
     </row>
     <row r="2" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="108"/>
+      <c r="B2" s="109"/>
       <c r="C2" s="6">
         <v>1</v>
       </c>
@@ -4024,10 +4012,10 @@
       </c>
     </row>
     <row r="3" spans="1:52" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="109" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="110"/>
+      <c r="A3" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111"/>
       <c r="C3" s="48">
         <v>45887</v>
       </c>
@@ -4171,7 +4159,7 @@
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="103" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4226,7 +4214,7 @@
       <c r="AW4" s="38"/>
     </row>
     <row r="5" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="102"/>
+      <c r="A5" s="103"/>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4285,7 +4273,7 @@
       <c r="AW5" s="34"/>
     </row>
     <row r="6" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="103"/>
+      <c r="A6" s="104"/>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
@@ -4337,14 +4325,14 @@
       <c r="AV6" s="35"/>
       <c r="AW6" s="36"/>
       <c r="AY6" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ6" s="76" t="s">
         <v>22</v>
-      </c>
-      <c r="AZ6" s="76" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="102" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4408,7 +4396,7 @@
       </c>
     </row>
     <row r="8" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="102"/>
+      <c r="A8" s="103"/>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
@@ -4476,7 +4464,7 @@
       </c>
     </row>
     <row r="9" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="103"/>
+      <c r="A9" s="104"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -4536,7 +4524,7 @@
       </c>
     </row>
     <row r="10" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="102" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4599,7 +4587,7 @@
       </c>
     </row>
     <row r="11" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="102"/>
+      <c r="A11" s="103"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -4671,7 +4659,7 @@
       </c>
     </row>
     <row r="12" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="103"/>
+      <c r="A12" s="104"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -4731,7 +4719,7 @@
       </c>
     </row>
     <row r="13" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="101" t="s">
+      <c r="A13" s="102" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -4793,7 +4781,7 @@
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A14" s="102"/>
+      <c r="A14" s="103"/>
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
@@ -4849,7 +4837,7 @@
       <c r="AW14" s="34"/>
     </row>
     <row r="15" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="103"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
@@ -4876,8 +4864,8 @@
       <c r="W15" s="61"/>
       <c r="X15" s="22"/>
       <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
-      <c r="AA15" s="22"/>
+      <c r="Z15" s="101"/>
+      <c r="AA15" s="101"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="40"/>
       <c r="AD15" s="58"/>
@@ -4902,7 +4890,7 @@
       <c r="AW15" s="36"/>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A16" s="101" t="s">
+      <c r="A16" s="102" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4957,7 +4945,7 @@
       <c r="AW16" s="38"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A17" s="102"/>
+      <c r="A17" s="103"/>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
@@ -5048,7 +5036,7 @@
       <c r="AW17" s="34"/>
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="103"/>
+      <c r="A18" s="104"/>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
@@ -5069,18 +5057,18 @@
       <c r="Q18" s="20"/>
       <c r="R18" s="100"/>
       <c r="S18" s="100"/>
-      <c r="T18" s="20"/>
-      <c r="U18" s="20"/>
+      <c r="T18" s="100"/>
+      <c r="U18" s="100"/>
       <c r="V18" s="40"/>
       <c r="W18" s="40"/>
-      <c r="X18" s="20"/>
-      <c r="Y18" s="20"/>
-      <c r="Z18" s="20"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
       <c r="AA18" s="20"/>
-      <c r="AB18" s="20"/>
-      <c r="AC18" s="40"/>
+      <c r="AB18" s="100"/>
+      <c r="AC18" s="100"/>
       <c r="AD18" s="40"/>
-      <c r="AE18" s="20"/>
+      <c r="AE18" s="100"/>
       <c r="AF18" s="20"/>
       <c r="AG18" s="20"/>
       <c r="AH18" s="20"/>
@@ -5101,7 +5089,7 @@
       <c r="AW18" s="36"/>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A19" s="101" t="s">
+      <c r="A19" s="102" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -5156,7 +5144,7 @@
       <c r="AW19" s="38"/>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A20" s="102"/>
+      <c r="A20" s="103"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
@@ -5225,7 +5213,7 @@
       <c r="AW20" s="34"/>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="103"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
@@ -5254,7 +5242,7 @@
       <c r="Y21" s="20"/>
       <c r="Z21" s="22"/>
       <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
+      <c r="AB21" s="121"/>
       <c r="AC21" s="40"/>
       <c r="AD21" s="58"/>
       <c r="AE21" s="20"/>
@@ -5278,7 +5266,7 @@
       <c r="AW21" s="36"/>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A22" s="101" t="s">
+      <c r="A22" s="102" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -5335,7 +5323,7 @@
       <c r="AW22" s="38"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A23" s="102"/>
+      <c r="A23" s="103"/>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
@@ -5442,7 +5430,7 @@
       <c r="AW23" s="34"/>
     </row>
     <row r="24" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="103"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
@@ -5466,14 +5454,14 @@
       <c r="T24" s="20"/>
       <c r="U24" s="20"/>
       <c r="V24" s="40"/>
-      <c r="W24" s="40"/>
-      <c r="X24" s="20"/>
+      <c r="W24" s="99"/>
+      <c r="X24" s="99"/>
       <c r="Y24" s="20"/>
       <c r="Z24" s="20"/>
       <c r="AA24" s="20"/>
       <c r="AB24" s="20"/>
       <c r="AC24" s="40"/>
-      <c r="AD24" s="40"/>
+      <c r="AD24" s="99"/>
       <c r="AE24" s="20"/>
       <c r="AF24" s="20"/>
       <c r="AG24" s="20"/>
@@ -5495,7 +5483,7 @@
       <c r="AW24" s="36"/>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A25" s="101" t="s">
+      <c r="A25" s="102" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -5552,7 +5540,7 @@
       <c r="AW25" s="38"/>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A26" s="102"/>
+      <c r="A26" s="103"/>
       <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
@@ -5605,7 +5593,7 @@
       <c r="AW26" s="75"/>
     </row>
     <row r="27" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="103"/>
+      <c r="A27" s="104"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -5658,7 +5646,7 @@
       <c r="AW27" s="36"/>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A28" s="101" t="s">
+      <c r="A28" s="102" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -5715,7 +5703,7 @@
       <c r="AW28" s="38"/>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A29" s="102"/>
+      <c r="A29" s="103"/>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
@@ -5768,7 +5756,7 @@
       <c r="AW29" s="34"/>
     </row>
     <row r="30" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="103"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
@@ -5821,8 +5809,8 @@
       <c r="AW30" s="36"/>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A31" s="101" t="s">
-        <v>21</v>
+      <c r="A31" s="102" t="s">
+        <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>13</v>
@@ -5878,7 +5866,7 @@
       <c r="AW31" s="38"/>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A32" s="102"/>
+      <c r="A32" s="103"/>
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -5931,7 +5919,7 @@
       <c r="AW32" s="34"/>
     </row>
     <row r="33" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="104"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>

--- a/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
+++ b/doc/2.Document Annexe/PLANIF_2510_RegulationChauffage_Mendes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/2.Document Annexe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="534" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCAF0FC9-D685-4945-BDBE-CF431906686D}"/>
+  <xr:revisionPtr revIDLastSave="541" documentId="13_ncr:1_{00258E3D-1571-498F-B005-0D98775A2B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{780691F0-A52E-4C31-AC02-14FEF534EDF7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6750" yWindow="2355" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1129,6 +1129,36 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1158,36 +1188,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1613,7 +1613,7 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>27</c:v>
@@ -3520,6 +3520,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -3822,77 +3826,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="115">
-        <v>1</v>
-      </c>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="117"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="106">
+        <v>1</v>
+      </c>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="108"/>
       <c r="H1" s="53"/>
       <c r="I1" s="54"/>
-      <c r="J1" s="115">
+      <c r="J1" s="106">
         <v>2</v>
       </c>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="117"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="108"/>
       <c r="O1" s="53"/>
       <c r="P1" s="54"/>
-      <c r="Q1" s="115">
+      <c r="Q1" s="106">
         <v>3</v>
       </c>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="117"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="108"/>
       <c r="V1" s="53"/>
       <c r="W1" s="54"/>
-      <c r="X1" s="115">
+      <c r="X1" s="106">
         <v>4</v>
       </c>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="117"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="108"/>
       <c r="AC1" s="53"/>
       <c r="AD1" s="54"/>
-      <c r="AE1" s="118">
+      <c r="AE1" s="109">
         <v>5</v>
       </c>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="120"/>
+      <c r="AF1" s="110"/>
+      <c r="AG1" s="110"/>
+      <c r="AH1" s="110"/>
+      <c r="AI1" s="111"/>
       <c r="AJ1" s="62"/>
       <c r="AK1" s="63"/>
-      <c r="AL1" s="112">
+      <c r="AL1" s="103">
         <v>6</v>
       </c>
-      <c r="AM1" s="113"/>
-      <c r="AN1" s="113"/>
-      <c r="AO1" s="113"/>
-      <c r="AP1" s="114"/>
+      <c r="AM1" s="104"/>
+      <c r="AN1" s="104"/>
+      <c r="AO1" s="104"/>
+      <c r="AP1" s="105"/>
       <c r="AQ1" s="62"/>
       <c r="AR1" s="63"/>
-      <c r="AS1" s="112">
+      <c r="AS1" s="103">
         <v>7</v>
       </c>
-      <c r="AT1" s="113"/>
-      <c r="AU1" s="113"/>
-      <c r="AV1" s="113"/>
-      <c r="AW1" s="114"/>
+      <c r="AT1" s="104"/>
+      <c r="AU1" s="104"/>
+      <c r="AV1" s="104"/>
+      <c r="AW1" s="105"/>
     </row>
     <row r="2" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="118" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="109"/>
+      <c r="B2" s="119"/>
       <c r="C2" s="6">
         <v>1</v>
       </c>
@@ -4012,10 +4016,10 @@
       </c>
     </row>
     <row r="3" spans="1:52" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="110" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="111"/>
+      <c r="A3" s="120" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="48">
         <v>45887</v>
       </c>
@@ -4159,7 +4163,7 @@
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A4" s="103" t="s">
+      <c r="A4" s="113" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -4214,7 +4218,7 @@
       <c r="AW4" s="38"/>
     </row>
     <row r="5" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="103"/>
+      <c r="A5" s="113"/>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4273,7 +4277,7 @@
       <c r="AW5" s="34"/>
     </row>
     <row r="6" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="104"/>
+      <c r="A6" s="114"/>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
@@ -4332,7 +4336,7 @@
       </c>
     </row>
     <row r="7" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="102" t="s">
+      <c r="A7" s="112" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4396,7 +4400,7 @@
       </c>
     </row>
     <row r="8" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="103"/>
+      <c r="A8" s="113"/>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
@@ -4464,7 +4468,7 @@
       </c>
     </row>
     <row r="9" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="104"/>
+      <c r="A9" s="114"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -4524,7 +4528,7 @@
       </c>
     </row>
     <row r="10" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="102" t="s">
+      <c r="A10" s="112" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4587,7 +4591,7 @@
       </c>
     </row>
     <row r="11" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="103"/>
+      <c r="A11" s="113"/>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
@@ -4659,7 +4663,7 @@
       </c>
     </row>
     <row r="12" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="104"/>
+      <c r="A12" s="114"/>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
@@ -4715,11 +4719,11 @@
       </c>
       <c r="AZ12" s="76">
         <f>SUM(C20:AW20)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="102" t="s">
+      <c r="A13" s="112" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -4781,7 +4785,7 @@
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A14" s="103"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
@@ -4837,7 +4841,7 @@
       <c r="AW14" s="34"/>
     </row>
     <row r="15" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="104"/>
+      <c r="A15" s="114"/>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
@@ -4890,7 +4894,7 @@
       <c r="AW15" s="36"/>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A16" s="102" t="s">
+      <c r="A16" s="112" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4945,7 +4949,7 @@
       <c r="AW16" s="38"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A17" s="103"/>
+      <c r="A17" s="113"/>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
@@ -5036,7 +5040,7 @@
       <c r="AW17" s="34"/>
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="104"/>
+      <c r="A18" s="114"/>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
@@ -5069,9 +5073,9 @@
       <c r="AC18" s="100"/>
       <c r="AD18" s="40"/>
       <c r="AE18" s="100"/>
-      <c r="AF18" s="20"/>
-      <c r="AG18" s="20"/>
-      <c r="AH18" s="20"/>
+      <c r="AF18" s="100"/>
+      <c r="AG18" s="100"/>
+      <c r="AH18" s="100"/>
       <c r="AI18" s="21"/>
       <c r="AJ18" s="68"/>
       <c r="AK18" s="68"/>
@@ -5089,7 +5093,7 @@
       <c r="AW18" s="36"/>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A19" s="102" t="s">
+      <c r="A19" s="112" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -5144,7 +5148,7 @@
       <c r="AW19" s="38"/>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A20" s="103"/>
+      <c r="A20" s="113"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
@@ -5195,7 +5199,9 @@
         <v>1</v>
       </c>
       <c r="AG20" s="25"/>
-      <c r="AH20" s="25"/>
+      <c r="AH20" s="86">
+        <v>1</v>
+      </c>
       <c r="AI20" s="27"/>
       <c r="AJ20" s="67"/>
       <c r="AK20" s="67"/>
@@ -5213,7 +5219,7 @@
       <c r="AW20" s="34"/>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="104"/>
+      <c r="A21" s="114"/>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
@@ -5242,7 +5248,7 @@
       <c r="Y21" s="20"/>
       <c r="Z21" s="22"/>
       <c r="AA21" s="20"/>
-      <c r="AB21" s="121"/>
+      <c r="AB21" s="102"/>
       <c r="AC21" s="40"/>
       <c r="AD21" s="58"/>
       <c r="AE21" s="20"/>
@@ -5266,7 +5272,7 @@
       <c r="AW21" s="36"/>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A22" s="102" t="s">
+      <c r="A22" s="112" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -5323,7 +5329,7 @@
       <c r="AW22" s="38"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A23" s="103"/>
+      <c r="A23" s="113"/>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
@@ -5430,7 +5436,7 @@
       <c r="AW23" s="34"/>
     </row>
     <row r="24" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="104"/>
+      <c r="A24" s="114"/>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
@@ -5465,9 +5471,9 @@
       <c r="AE24" s="20"/>
       <c r="AF24" s="20"/>
       <c r="AG24" s="20"/>
-      <c r="AH24" s="20"/>
-      <c r="AI24" s="21"/>
-      <c r="AJ24" s="68"/>
+      <c r="AH24" s="99"/>
+      <c r="AI24" s="99"/>
+      <c r="AJ24" s="99"/>
       <c r="AK24" s="68"/>
       <c r="AL24" s="35"/>
       <c r="AM24" s="35"/>
@@ -5483,7 +5489,7 @@
       <c r="AW24" s="36"/>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A25" s="102" t="s">
+      <c r="A25" s="112" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -5540,7 +5546,7 @@
       <c r="AW25" s="38"/>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A26" s="103"/>
+      <c r="A26" s="113"/>
       <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
@@ -5593,7 +5599,7 @@
       <c r="AW26" s="75"/>
     </row>
     <row r="27" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="104"/>
+      <c r="A27" s="114"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -5646,7 +5652,7 @@
       <c r="AW27" s="36"/>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A28" s="102" t="s">
+      <c r="A28" s="112" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -5703,7 +5709,7 @@
       <c r="AW28" s="38"/>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A29" s="103"/>
+      <c r="A29" s="113"/>
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
@@ -5756,7 +5762,7 @@
       <c r="AW29" s="34"/>
     </row>
     <row r="30" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="104"/>
+      <c r="A30" s="114"/>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
@@ -5809,7 +5815,7 @@
       <c r="AW30" s="36"/>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A31" s="102" t="s">
+      <c r="A31" s="112" t="s">
         <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -5866,7 +5872,7 @@
       <c r="AW31" s="38"/>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A32" s="103"/>
+      <c r="A32" s="113"/>
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -5919,7 +5925,7 @@
       <c r="AW32" s="34"/>
     </row>
     <row r="33" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="105"/>
+      <c r="A33" s="115"/>
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
@@ -6004,13 +6010,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AL1:AP1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
@@ -6024,6 +6023,13 @@
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A19:A21"/>
+    <mergeCell ref="AL1:AP1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="X1:AB1"/>
+    <mergeCell ref="AE1:AI1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6051,6 +6057,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D4F20F00DBE2EE49BE9523363A2DF18B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="508407daaf082c5381f5a7b4d9841321">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99ffe1f3-7857-457f-add0-5bdef636f38d" xmlns:ns3="be0d3259-a7ce-4623-88ec-81594dfcbc1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d41ad40f3ea4d0f4b8e18c6becc727c2" ns2:_="" ns3:_="">
     <xsd:import namespace="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
@@ -6285,27 +6311,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="be0d3259-a7ce-4623-88ec-81594dfcbc1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="99ffe1f3-7857-457f-add0-5bdef636f38d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D3E6B6-1954-499D-AE9A-4487E5EEA9C5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6322,29 +6353,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD04FC36-9477-4112-8B1B-E85999D4529A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CA8A74-E392-4C76-B4A8-766BFA7BB5FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>